--- a/data.xlsx
+++ b/data.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,19 +539,15 @@
           <t>10/05/26 07:00 am</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>COMDC - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>22 days, 16:26:56.646705</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -603,12 +599,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646638</t>
+          <t>21 days, 15:44:42.352168</t>
         </is>
       </c>
     </row>
@@ -660,12 +656,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646590</t>
+          <t>21 days, 15:44:42.352113</t>
         </is>
       </c>
     </row>
@@ -717,12 +713,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646549</t>
+          <t>21 days, 15:44:42.352074</t>
         </is>
       </c>
     </row>
@@ -774,12 +770,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646508</t>
+          <t>21 days, 15:44:42.352035</t>
         </is>
       </c>
     </row>
@@ -831,12 +827,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646466</t>
+          <t>21 days, 15:44:42.352000</t>
         </is>
       </c>
     </row>
@@ -888,12 +884,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646428</t>
+          <t>21 days, 15:44:42.351968</t>
         </is>
       </c>
     </row>
@@ -945,12 +941,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646391</t>
+          <t>21 days, 15:44:42.351937</t>
         </is>
       </c>
     </row>
@@ -997,17 +993,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646355</t>
+          <t>21 days, 15:44:42.351908</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1050,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646318</t>
+          <t>21 days, 15:44:42.351878</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1112,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646283</t>
+          <t>21 days, 15:44:42.351848</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1169,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22 days, 16:26:56.646247</t>
+          <t>21 days, 15:44:42.351819</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1231,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20 days, 2:26:56.646206</t>
+          <t>19 days, 1:44:42.351785</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1293,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>20 days, 2:26:56.646165</t>
+          <t>19 days, 1:44:42.351750</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1346,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -1402,17 +1398,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.646075</t>
+          <t>18 days, 17:59:42.351682</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1455,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.646038</t>
+          <t>18 days, 17:59:42.351652</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1512,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.646005</t>
+          <t>18 days, 17:59:42.351624</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1569,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645947</t>
+          <t>18 days, 17:59:42.351593</t>
         </is>
       </c>
     </row>
@@ -1630,17 +1626,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645907</t>
+          <t>18 days, 17:59:42.351565</t>
         </is>
       </c>
     </row>
@@ -1687,17 +1683,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645870</t>
+          <t>18 days, 17:59:42.351536</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1740,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645836</t>
+          <t>18 days, 17:59:42.351508</t>
         </is>
       </c>
     </row>
@@ -1801,17 +1797,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645800</t>
+          <t>18 days, 17:59:42.351480</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1854,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645767</t>
+          <t>18 days, 17:59:42.351451</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1911,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645732</t>
+          <t>18 days, 17:59:42.351419</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1968,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645698</t>
+          <t>18 days, 17:59:42.351391</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2025,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645664</t>
+          <t>18 days, 17:59:42.351363</t>
         </is>
       </c>
     </row>
@@ -2086,17 +2082,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645629</t>
+          <t>18 days, 17:59:42.351335</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2139,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645594</t>
+          <t>18 days, 17:59:42.351305</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2196,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645561</t>
+          <t>18 days, 17:59:42.351277</t>
         </is>
       </c>
     </row>
@@ -2257,17 +2253,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645528</t>
+          <t>18 days, 17:59:42.351225</t>
         </is>
       </c>
     </row>
@@ -2314,17 +2310,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645493</t>
+          <t>18 days, 17:59:42.351190</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2367,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645461</t>
+          <t>18 days, 17:59:42.351162</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2424,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645428</t>
+          <t>18 days, 17:59:42.351134</t>
         </is>
       </c>
     </row>
@@ -2485,17 +2481,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645397</t>
+          <t>18 days, 17:59:42.351107</t>
         </is>
       </c>
     </row>
@@ -2542,17 +2538,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645365</t>
+          <t>18 days, 17:59:42.351079</t>
         </is>
       </c>
     </row>
@@ -2599,17 +2595,17 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645335</t>
+          <t>18 days, 17:59:42.351051</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2652,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645304</t>
+          <t>18 days, 17:59:42.351024</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2714,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 18:41:56.645269</t>
+          <t>18 days, 17:59:42.350996</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2771,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645225</t>
+          <t>18 days, 17:29:42.350957</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2828,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645181</t>
+          <t>18 days, 17:29:42.350921</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2885,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645139</t>
+          <t>18 days, 17:29:42.350886</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2942,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645096</t>
+          <t>18 days, 17:29:42.350848</t>
         </is>
       </c>
     </row>
@@ -3003,12 +2999,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645053</t>
+          <t>18 days, 17:29:42.350809</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3056,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.645011</t>
+          <t>18 days, 17:29:42.350771</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3113,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.644939</t>
+          <t>18 days, 17:29:42.350736</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3170,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19 days, 18:11:56.644880</t>
+          <t>18 days, 17:29:42.350698</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3223,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3276,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3333,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644750</t>
+          <t>17 days, 21:44:42.350592</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3390,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644706</t>
+          <t>17 days, 21:44:42.350556</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3447,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644661</t>
+          <t>17 days, 21:44:42.350521</t>
         </is>
       </c>
     </row>
@@ -3508,12 +3504,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644616</t>
+          <t>17 days, 21:44:42.350484</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3561,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644572</t>
+          <t>17 days, 21:44:42.350447</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3618,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644526</t>
+          <t>17 days, 21:44:42.350408</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3675,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644486</t>
+          <t>17 days, 21:44:42.350374</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3732,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644446</t>
+          <t>17 days, 21:44:42.350340</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3789,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644403</t>
+          <t>17 days, 21:44:42.350303</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3846,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 22:26:56.644363</t>
+          <t>17 days, 21:44:42.350270</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3903,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644326</t>
+          <t>17 days, 21:14:42.350227</t>
         </is>
       </c>
     </row>
@@ -3964,12 +3960,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644289</t>
+          <t>17 days, 21:14:42.350196</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4017,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644253</t>
+          <t>17 days, 21:14:42.350167</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4074,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644218</t>
+          <t>17 days, 21:14:42.350137</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4131,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644182</t>
+          <t>17 days, 21:14:42.350107</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4188,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644147</t>
+          <t>17 days, 21:14:42.350078</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4245,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644111</t>
+          <t>17 days, 21:14:42.350048</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4302,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644076</t>
+          <t>17 days, 21:14:42.350018</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4359,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644040</t>
+          <t>17 days, 21:14:42.349988</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4416,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.644005</t>
+          <t>17 days, 21:14:42.349958</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4473,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.643941</t>
+          <t>17 days, 21:14:42.349923</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4530,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.643898</t>
+          <t>17 days, 21:14:42.349891</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4587,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.643857</t>
+          <t>17 days, 21:14:42.349858</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4644,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>18 days, 21:56:56.643820</t>
+          <t>17 days, 21:14:42.349827</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4706,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643780</t>
+          <t>17 days, 18:59:42.349793</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4768,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643741</t>
+          <t>17 days, 18:59:42.349760</t>
         </is>
       </c>
     </row>
@@ -4834,12 +4830,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643700</t>
+          <t>17 days, 18:59:42.349726</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4892,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643660</t>
+          <t>17 days, 18:59:42.349692</t>
         </is>
       </c>
     </row>
@@ -4958,12 +4954,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643620</t>
+          <t>17 days, 18:59:42.349658</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5016,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643580</t>
+          <t>17 days, 18:59:42.349624</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5078,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643540</t>
+          <t>17 days, 18:59:42.349590</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5140,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643500</t>
+          <t>17 days, 18:59:42.349557</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5202,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643461</t>
+          <t>17 days, 18:59:42.349525</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5264,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643422</t>
+          <t>17 days, 18:59:42.349492</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5326,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643384</t>
+          <t>17 days, 18:59:42.349459</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5388,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643346</t>
+          <t>17 days, 18:59:42.349427</t>
         </is>
       </c>
     </row>
@@ -5454,12 +5450,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643307</t>
+          <t>17 days, 18:59:42.349393</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5512,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643268</t>
+          <t>17 days, 18:59:42.349358</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5574,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643229</t>
+          <t>17 days, 18:59:42.349324</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5636,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643190</t>
+          <t>17 days, 18:59:42.349291</t>
         </is>
       </c>
     </row>
@@ -5702,12 +5698,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>18 days, 19:41:56.643152</t>
+          <t>17 days, 18:59:42.349259</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5751,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5809,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -5871,12 +5867,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5894,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5926,19 +5922,15 @@
           <t>09/30/26 11:45 am</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>WGL07 - 24-hour delay</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>17 days, 21:11:56.643019</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -5991,12 +5983,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6049,12 +6041,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6107,12 +6099,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6169,12 +6161,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>17 days, 21:11:56.642843</t>
+          <t>16 days, 20:29:42.349050</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6219,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6285,12 +6277,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6343,12 +6335,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6401,12 +6393,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6451,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6509,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6567,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6625,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6683,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6710,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6746,19 +6738,15 @@
           <t>09/30/26 08:00 am</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>WGL07 - 24-hour delay</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>17 days, 17:26:56.642551</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -6810,12 +6798,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>17 days, 17:11:56.642509</t>
+          <t>16 days, 16:29:42.348788</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6855,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>17 days, 17:11:56.642472</t>
+          <t>16 days, 16:29:42.348757</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6908,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>17 days, 0:26:56.642430</t>
+          <t>15 days, 23:44:42.348721</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6961,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7018,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>16 days, 19:41:56.642359</t>
+          <t>15 days, 18:59:42.348664</t>
         </is>
       </c>
     </row>
@@ -7083,12 +7071,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7136,12 +7124,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7177,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7230,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7295,12 +7283,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7336,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7389,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7442,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7499,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>16 days, 19:41:56.642094</t>
+          <t>15 days, 18:59:42.348439</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7556,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>16 days, 19:26:56.642055</t>
+          <t>15 days, 18:44:42.348406</t>
         </is>
       </c>
     </row>
@@ -7625,12 +7613,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>16 days, 19:26:56.642015</t>
+          <t>15 days, 18:44:42.348373</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7670,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>16 days, 19:26:56.641978</t>
+          <t>15 days, 18:44:42.348340</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7727,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>16 days, 19:26:56.641915</t>
+          <t>15 days, 18:44:42.348307</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7784,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>16 days, 19:26:56.641876</t>
+          <t>15 days, 18:44:42.348275</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7837,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7890,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -7955,12 +7943,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8008,12 +7996,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8049,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8102,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8167,12 +8155,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8208,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8261,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8314,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8367,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8432,12 +8420,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8485,12 +8473,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8526,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8579,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8644,12 +8632,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8685,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8738,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8791,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8856,12 +8844,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8897,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -8962,12 +8950,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9015,12 +9003,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9056,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9121,12 +9109,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9174,12 +9162,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9215,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9268,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9333,12 +9321,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9386,12 +9374,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9439,12 +9427,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9492,12 +9480,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9545,12 +9533,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9586,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9639,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9704,12 +9692,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9757,12 +9745,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9810,12 +9798,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9851,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9916,12 +9904,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -9969,12 +9957,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10022,12 +10010,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10063,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10128,12 +10116,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10181,12 +10169,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10234,12 +10222,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10287,12 +10275,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10328,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10381,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10446,12 +10434,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10487,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10552,12 +10540,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10593,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10658,12 +10646,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10711,12 +10699,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10764,12 +10752,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10817,12 +10805,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10870,12 +10858,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10923,12 +10911,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -10976,12 +10964,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11033,12 +11021,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.640072</t>
+          <t>10 days, 20:14:42.346760</t>
         </is>
       </c>
     </row>
@@ -11090,12 +11078,12 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.640037</t>
+          <t>10 days, 20:14:42.346732</t>
         </is>
       </c>
     </row>
@@ -11147,12 +11135,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.640004</t>
+          <t>10 days, 20:14:42.346705</t>
         </is>
       </c>
     </row>
@@ -11204,12 +11192,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.639954</t>
+          <t>10 days, 20:14:42.346678</t>
         </is>
       </c>
     </row>
@@ -11261,12 +11249,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.639915</t>
+          <t>10 days, 20:14:42.346651</t>
         </is>
       </c>
     </row>
@@ -11318,12 +11306,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>11 days, 20:56:56.639881</t>
+          <t>10 days, 20:14:42.346624</t>
         </is>
       </c>
     </row>
@@ -11371,12 +11359,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11429,12 +11417,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11487,12 +11475,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11545,12 +11533,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11603,12 +11591,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11644,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11709,12 +11697,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11767,12 +11755,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11825,12 +11813,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11883,12 +11871,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11941,12 +11929,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -11999,12 +11987,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12057,12 +12045,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12115,12 +12103,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12168,12 +12156,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12213,12 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>8 days, 19:26:56.639358</t>
+          <t>7 days, 18:44:42.346181</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12266,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12336,12 +12324,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12394,12 +12382,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12452,12 +12440,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12510,12 +12498,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12568,12 +12556,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12626,12 +12614,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12684,12 +12672,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12742,12 +12730,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12800,12 +12788,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12858,12 +12846,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12916,12 +12904,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -12974,12 +12962,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13032,12 +13020,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13090,12 +13078,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13148,12 +13136,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13206,12 +13194,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13252,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13322,12 +13310,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13380,12 +13368,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13438,12 +13426,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13496,12 +13484,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13542,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13612,12 +13600,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13670,12 +13658,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13728,12 +13716,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13786,12 +13774,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13844,12 +13832,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13902,12 +13890,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -13960,12 +13948,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14018,12 +14006,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14076,12 +14064,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14122,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14192,12 +14180,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14238,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14303,12 +14291,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14356,12 +14344,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14413,12 +14401,12 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>5 days, 19:26:56.638156</t>
+          <t>4 days, 18:44:42.345204</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14454,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14511,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>5 days, 19:26:56.638088</t>
+          <t>4 days, 18:44:42.345149</t>
         </is>
       </c>
     </row>
@@ -14576,12 +14564,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14629,12 +14617,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14670,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14735,12 +14723,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14788,12 +14776,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14829,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14894,12 +14882,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -14947,12 +14935,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15000,12 +14988,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15057,12 +15045,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>4 days, 22:11:56.637711</t>
+          <t>3 days, 21:29:42.344872</t>
         </is>
       </c>
     </row>
@@ -15115,12 +15103,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15168,12 +15156,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15221,12 +15209,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15274,12 +15262,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15327,12 +15315,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15380,12 +15368,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15433,12 +15421,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15491,12 +15479,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15549,12 +15537,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15602,12 +15590,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15643,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15708,12 +15696,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15761,12 +15749,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15814,12 +15802,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15867,12 +15855,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15920,12 +15908,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -15973,12 +15961,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16026,12 +16014,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16079,12 +16067,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16132,12 +16120,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16185,12 +16173,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16238,12 +16226,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16291,12 +16279,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16344,12 +16332,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16397,12 +16385,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16450,12 +16438,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16491,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16556,12 +16544,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16609,12 +16597,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16662,12 +16650,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16703,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16768,12 +16756,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16821,12 +16809,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16874,12 +16862,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16927,12 +16915,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -16980,12 +16968,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17033,12 +17021,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17086,12 +17074,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17139,12 +17127,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17196,12 +17184,12 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>4 days, 17:41:56.636452</t>
+          <t>3 days, 16:59:42.343846</t>
         </is>
       </c>
     </row>
@@ -17249,12 +17237,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17302,12 +17290,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17355,12 +17343,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17408,12 +17396,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17461,12 +17449,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17502,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17567,12 +17555,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17620,12 +17608,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17673,12 +17661,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17726,12 +17714,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17779,12 +17767,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17832,12 +17820,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17885,12 +17873,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17938,12 +17926,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -17991,12 +17979,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18044,12 +18032,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18097,12 +18085,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18150,12 +18138,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18203,12 +18191,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18256,12 +18244,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18309,12 +18297,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18362,12 +18350,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18415,12 +18403,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18468,12 +18456,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18521,12 +18509,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18574,12 +18562,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18627,12 +18615,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18680,12 +18668,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18733,12 +18721,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18786,12 +18774,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18839,12 +18827,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18892,12 +18880,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18945,12 +18933,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -18998,12 +18986,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19051,12 +19039,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19104,12 +19092,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19157,12 +19145,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19210,12 +19198,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19263,12 +19251,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19316,12 +19304,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19369,12 +19357,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19422,12 +19410,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19475,12 +19463,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19528,12 +19516,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19581,12 +19569,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19634,12 +19622,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19691,12 +19679,12 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>4 days, 17:11:56.635055</t>
+          <t>3 days, 16:29:42.342631</t>
         </is>
       </c>
     </row>
@@ -19744,12 +19732,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19797,12 +19785,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19850,12 +19838,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19903,12 +19891,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -19956,12 +19944,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20009,12 +19997,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20062,12 +20050,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20115,12 +20103,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20168,12 +20156,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20221,12 +20209,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20274,12 +20262,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20327,12 +20315,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20380,12 +20368,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20433,12 +20421,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20486,12 +20474,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20539,12 +20527,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20592,12 +20580,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20645,12 +20633,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20698,12 +20686,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20751,12 +20739,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20804,12 +20792,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20857,12 +20845,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20910,12 +20898,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20951,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21016,12 +21004,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21069,12 +21057,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21122,12 +21110,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21175,12 +21163,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21228,12 +21216,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21269,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21334,12 +21322,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21387,12 +21375,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21440,12 +21428,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21497,12 +21485,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>4 days, 16:41:56.634017</t>
+          <t>3 days, 15:59:42.341768</t>
         </is>
       </c>
     </row>
@@ -21550,12 +21538,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21603,12 +21591,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21656,12 +21644,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21709,12 +21697,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21762,12 +21750,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21815,12 +21803,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21868,12 +21856,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21921,12 +21909,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -21974,12 +21962,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22027,12 +22015,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22080,12 +22068,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22133,12 +22121,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22186,12 +22174,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22239,12 +22227,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22292,12 +22280,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22345,12 +22333,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22398,12 +22386,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22439,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22504,12 +22492,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22557,12 +22545,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22610,12 +22598,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22663,12 +22651,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22716,12 +22704,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22769,12 +22757,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22822,12 +22810,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22875,12 +22863,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22928,12 +22916,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -22981,12 +22969,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23039,12 +23027,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23097,12 +23085,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23155,12 +23143,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23213,12 +23201,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23271,12 +23259,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23329,12 +23317,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23391,12 +23379,12 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>3 days, 22:41:56.632857</t>
+          <t>2 days, 21:59:42.340832</t>
         </is>
       </c>
     </row>
@@ -23449,12 +23437,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23507,12 +23495,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23565,12 +23553,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23623,12 +23611,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23669,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23739,12 +23727,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23797,12 +23785,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23855,12 +23843,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23913,12 +23901,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -23971,12 +23959,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24029,12 +24017,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24087,12 +24075,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24145,12 +24133,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24203,12 +24191,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24261,12 +24249,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24319,12 +24307,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24377,12 +24365,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24435,12 +24423,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24493,12 +24481,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24539,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24609,12 +24597,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24667,12 +24655,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24725,12 +24713,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24783,12 +24771,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24841,12 +24829,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24899,12 +24887,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -24957,12 +24945,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25015,12 +25003,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25073,12 +25061,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25131,12 +25119,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25189,12 +25177,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25247,12 +25235,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25305,12 +25293,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25363,12 +25351,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25409,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25479,12 +25467,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25537,12 +25525,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25595,12 +25583,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25653,12 +25641,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25711,12 +25699,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25769,12 +25757,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25827,12 +25815,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25885,12 +25873,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -25943,12 +25931,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26001,12 +25989,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26059,12 +26047,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26117,12 +26105,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26175,12 +26163,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26233,12 +26221,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26291,12 +26279,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26349,12 +26337,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26407,12 +26395,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26465,12 +26453,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26523,12 +26511,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26581,12 +26569,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26639,12 +26627,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26697,12 +26685,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26754,12 +26742,12 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>3 days, 21:56:56.631140</t>
+          <t>2 days, 21:14:42.339396</t>
         </is>
       </c>
     </row>
@@ -26811,12 +26799,12 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>3 days, 21:56:56.631095</t>
+          <t>2 days, 21:14:42.339358</t>
         </is>
       </c>
     </row>
@@ -26864,12 +26852,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26917,12 +26905,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -26970,12 +26958,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27028,12 +27016,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27086,12 +27074,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27144,12 +27132,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27202,12 +27190,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27260,12 +27248,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27318,12 +27306,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27376,12 +27364,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27434,12 +27422,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27492,12 +27480,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27550,12 +27538,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27607,12 +27595,12 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>3 days, 16:26:56.630572</t>
+          <t>2 days, 15:44:42.338963</t>
         </is>
       </c>
     </row>
@@ -27664,12 +27652,12 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>3 days, 16:26:56.630532</t>
+          <t>2 days, 15:44:42.338930</t>
         </is>
       </c>
     </row>
@@ -27717,12 +27705,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27770,12 +27758,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27823,12 +27811,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27876,12 +27864,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27929,12 +27917,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -27982,12 +27970,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28035,12 +28023,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28088,12 +28076,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28141,12 +28129,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28198,12 +28186,12 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>2 days, 21:11:56.630225</t>
+          <t>1 day, 20:29:42.338675</t>
         </is>
       </c>
     </row>
@@ -28251,12 +28239,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28304,12 +28292,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28357,12 +28345,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28410,12 +28398,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28463,12 +28451,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28516,12 +28504,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28569,12 +28557,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28622,12 +28610,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28675,12 +28663,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28728,12 +28716,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28785,12 +28773,12 @@
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>2 days, 20:26:56.629909</t>
+          <t>1 day, 19:44:42.338432</t>
         </is>
       </c>
     </row>
@@ -28838,12 +28826,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28891,12 +28879,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28944,12 +28932,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -28997,12 +28985,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29050,12 +29038,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29103,12 +29091,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29156,12 +29144,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29209,12 +29197,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29262,12 +29250,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29315,12 +29303,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29368,12 +29356,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29421,12 +29409,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29474,12 +29462,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29527,12 +29515,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29580,12 +29568,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29633,12 +29621,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29686,12 +29674,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29739,12 +29727,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29792,12 +29780,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29845,12 +29833,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29898,12 +29886,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -29951,12 +29939,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30004,12 +29992,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30057,12 +30045,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30110,12 +30098,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30163,12 +30151,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30216,12 +30204,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30269,12 +30257,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30322,12 +30310,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30375,12 +30363,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30428,12 +30416,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30481,12 +30469,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30534,12 +30522,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30587,12 +30575,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30640,12 +30628,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30693,12 +30681,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30746,12 +30734,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30799,12 +30787,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30852,12 +30840,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30905,12 +30893,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -30958,12 +30946,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31011,12 +30999,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31064,12 +31052,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31117,12 +31105,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31170,12 +31158,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31223,12 +31211,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31276,12 +31264,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31329,12 +31317,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31382,12 +31370,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31435,12 +31423,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31488,12 +31476,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31541,12 +31529,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31594,12 +31582,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31647,12 +31635,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31700,12 +31688,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31753,12 +31741,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31806,12 +31794,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31859,12 +31847,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31912,12 +31900,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -31965,12 +31953,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32018,12 +32006,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32071,12 +32059,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32124,12 +32112,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32177,12 +32165,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32234,12 +32222,12 @@
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>2 days, 17:41:56.628040</t>
+          <t>1 day, 16:59:42.336711</t>
         </is>
       </c>
     </row>
@@ -32287,12 +32275,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32340,12 +32328,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32393,12 +32381,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32446,12 +32434,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32499,12 +32487,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32552,12 +32540,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32605,12 +32593,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32658,12 +32646,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32711,12 +32699,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32764,12 +32752,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32817,12 +32805,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32870,12 +32858,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32923,12 +32911,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -32976,12 +32964,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33029,12 +33017,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33082,12 +33070,12 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33135,12 +33123,12 @@
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33188,12 +33176,12 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33241,12 +33229,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33294,12 +33282,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33347,12 +33335,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33400,12 +33388,12 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33453,12 +33441,12 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33506,12 +33494,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33559,12 +33547,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33612,12 +33600,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33665,12 +33653,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33718,12 +33706,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33771,12 +33759,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33824,12 +33812,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33877,12 +33865,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33930,12 +33918,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -33983,12 +33971,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34036,12 +34024,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34089,12 +34077,12 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34142,12 +34130,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34195,12 +34183,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34248,12 +34236,12 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34301,12 +34289,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34354,12 +34342,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34407,12 +34395,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34460,12 +34448,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34513,12 +34501,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34566,12 +34554,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34619,12 +34607,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34681,12 +34669,12 @@
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>2 days, 16:26:56.626768</t>
+          <t>1 day, 15:44:42.335656</t>
         </is>
       </c>
     </row>
@@ -34734,12 +34722,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34787,12 +34775,12 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34840,12 +34828,12 @@
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34893,12 +34881,12 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -34950,12 +34938,12 @@
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>1 day, 22:26:56.626600</t>
+          <t>21:44:42.335517</t>
         </is>
       </c>
     </row>
@@ -35003,12 +34991,12 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35056,12 +35044,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35109,12 +35097,12 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35162,12 +35150,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35215,12 +35203,12 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35268,12 +35256,12 @@
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35321,12 +35309,12 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35378,12 +35366,12 @@
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>1 day, 22:11:56.626360</t>
+          <t>21:29:42.335315</t>
         </is>
       </c>
     </row>
@@ -35435,12 +35423,12 @@
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t>1 day, 22:11:56.626327</t>
+          <t>21:29:42.335288</t>
         </is>
       </c>
     </row>
@@ -35488,12 +35476,12 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35541,12 +35529,12 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35594,12 +35582,12 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35647,12 +35635,12 @@
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35704,12 +35692,12 @@
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>1 day, 22:11:56.626174</t>
+          <t>21:29:42.335147</t>
         </is>
       </c>
     </row>
@@ -35761,12 +35749,12 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>1 day, 22:11:56.626140</t>
+          <t>21:29:42.335119</t>
         </is>
       </c>
     </row>
@@ -35819,12 +35807,12 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35877,12 +35865,12 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35935,12 +35923,12 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -35993,12 +35981,12 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>
@@ -36051,12 +36039,12 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>09/11/26 02:33 PM</t>
+          <t>09/12/26 03:15 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20 days, 1:54:14.440166</t>
+          <t>19 days, 1:35:18.434648</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20 days, 1:54:14.440099</t>
+          <t>19 days, 1:35:18.434582</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20 days, 1:54:14.440051</t>
+          <t>19 days, 1:35:18.434535</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20 days, 1:54:14.440007</t>
+          <t>19 days, 1:35:18.434489</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20 days, 1:54:14.439966</t>
+          <t>19 days, 1:35:18.434449</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20 days, 0:54:14.439925</t>
+          <t>19 days, 0:35:18.434406</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 days, 0:54:14.439845</t>
+          <t>19 days, 0:35:18.434365</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20 days, 0:54:14.439800</t>
+          <t>19 days, 0:35:18.434325</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20 days, 0:54:14.439759</t>
+          <t>19 days, 0:35:18.434285</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19 days, 22:24:14.439666</t>
+          <t>18 days, 22:05:18.434194</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 21:24:14.439591</t>
+          <t>18 days, 21:05:18.434119</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 21:24:14.439555</t>
+          <t>18 days, 21:05:18.434082</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 21:24:14.439521</t>
+          <t>18 days, 21:05:18.434048</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 21:39:14.439481</t>
+          <t>18 days, 21:20:18.434008</t>
         </is>
       </c>
     </row>
@@ -1457,17 +1457,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 21:39:14.439442</t>
+          <t>18 days, 21:20:18.433940</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 19:24:14.439406</t>
+          <t>18 days, 19:05:18.433885</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 19:24:14.439372</t>
+          <t>18 days, 19:05:18.433851</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>18 days, 21:24:14.439300</t>
+          <t>17 days, 21:05:18.433779</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18 days, 18:09:14.439263</t>
+          <t>17 days, 17:50:18.433742</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>18 days, 16:54:14.439225</t>
+          <t>17 days, 16:35:18.433703</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>18 days, 16:54:14.439189</t>
+          <t>17 days, 16:35:18.433660</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.439081</t>
+          <t>17 days, 0:05:18.433542</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.439043</t>
+          <t>17 days, 0:05:18.433503</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.439005</t>
+          <t>17 days, 0:05:18.433465</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.438968</t>
+          <t>17 days, 0:05:18.433427</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.438932</t>
+          <t>17 days, 0:05:18.433390</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18 days, 0:24:14.438869</t>
+          <t>17 days, 0:05:18.433352</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17 days, 17:54:14.438789</t>
+          <t>16 days, 17:35:18.433278</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438715</t>
+          <t>15 days, 20:35:18.433206</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438679</t>
+          <t>15 days, 20:35:18.433168</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438641</t>
+          <t>15 days, 20:35:18.433130</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438606</t>
+          <t>15 days, 20:35:18.433089</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438565</t>
+          <t>15 days, 20:35:18.433048</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16 days, 20:54:14.438530</t>
+          <t>15 days, 20:35:18.433012</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2908,12 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2961,12 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3173,12 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3385,12 +3385,12 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3438,12 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3650,12 +3650,12 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3862,12 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -3968,12 +3968,12 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4339,12 +4339,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>16 days, 18:39:14.437685</t>
+          <t>15 days, 18:20:18.432150</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437648</t>
+          <t>15 days, 18:05:18.432113</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437612</t>
+          <t>15 days, 18:05:18.432076</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437576</t>
+          <t>15 days, 18:05:18.432039</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437543</t>
+          <t>15 days, 18:05:18.432004</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437510</t>
+          <t>15 days, 18:05:18.431929</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437476</t>
+          <t>15 days, 18:05:18.431877</t>
         </is>
       </c>
     </row>
@@ -4795,12 +4795,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437443</t>
+          <t>15 days, 18:05:18.431840</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>16 days, 18:24:14.437409</t>
+          <t>15 days, 18:05:18.431803</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -4958,12 +4958,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5011,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5064,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5223,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5450,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5566,12 +5566,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5682,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5798,12 +5798,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>16 days, 1:24:14.436805</t>
+          <t>15 days, 1:05:18.431200</t>
         </is>
       </c>
     </row>
@@ -5976,12 +5976,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6034,12 +6034,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6092,12 +6092,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6266,12 +6266,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>15 days, 21:24:14.436508</t>
+          <t>14 days, 21:05:18.430863</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6676,12 +6676,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6792,12 +6792,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6850,12 +6850,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6908,12 +6908,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -6966,12 +6966,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7082,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7140,12 +7140,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7256,12 +7256,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7372,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7430,12 +7430,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7662,12 +7662,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7778,12 +7778,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7836,12 +7836,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -7952,12 +7952,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8068,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8184,12 +8184,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8358,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8416,12 +8416,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8532,12 +8532,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8648,12 +8648,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8764,12 +8764,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8880,12 +8880,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8938,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435271</t>
+          <t>14 days, 20:50:18.429618</t>
         </is>
       </c>
     </row>
@@ -9062,12 +9062,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435228</t>
+          <t>14 days, 20:50:18.429574</t>
         </is>
       </c>
     </row>
@@ -9124,12 +9124,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435180</t>
+          <t>14 days, 20:50:18.429534</t>
         </is>
       </c>
     </row>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435143</t>
+          <t>14 days, 20:50:18.429497</t>
         </is>
       </c>
     </row>
@@ -9248,12 +9248,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435100</t>
+          <t>14 days, 20:50:18.429457</t>
         </is>
       </c>
     </row>
@@ -9310,12 +9310,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435061</t>
+          <t>14 days, 20:50:18.429418</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.435022</t>
+          <t>14 days, 20:50:18.429378</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434986</t>
+          <t>14 days, 20:50:18.429342</t>
         </is>
       </c>
     </row>
@@ -9496,12 +9496,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434945</t>
+          <t>14 days, 20:50:18.429300</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434889</t>
+          <t>14 days, 20:50:18.429262</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434846</t>
+          <t>14 days, 20:50:18.429223</t>
         </is>
       </c>
     </row>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434806</t>
+          <t>14 days, 20:50:18.429184</t>
         </is>
       </c>
     </row>
@@ -9744,12 +9744,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434764</t>
+          <t>14 days, 20:50:18.429144</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9806,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434721</t>
+          <t>14 days, 20:50:18.429102</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>15 days, 21:09:14.434680</t>
+          <t>14 days, 20:50:18.429062</t>
         </is>
       </c>
     </row>
@@ -9921,12 +9921,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10027,12 +10027,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10080,12 +10080,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10133,12 +10133,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10239,12 +10239,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10345,12 +10345,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>15 days, 19:09:14.434387</t>
+          <t>14 days, 18:50:18.428730</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10508,12 +10508,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>15 days, 18:09:14.434267</t>
+          <t>14 days, 17:50:18.428609</t>
         </is>
       </c>
     </row>
@@ -10675,12 +10675,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>15 days, 18:09:14.434230</t>
+          <t>14 days, 17:50:18.428572</t>
         </is>
       </c>
     </row>
@@ -10732,12 +10732,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>15 days, 18:09:14.434195</t>
+          <t>14 days, 17:50:18.428537</t>
         </is>
       </c>
     </row>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>15 days, 18:09:14.434161</t>
+          <t>14 days, 17:50:18.428503</t>
         </is>
       </c>
     </row>
@@ -10846,12 +10846,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>15 days, 18:09:14.434126</t>
+          <t>14 days, 17:50:18.428469</t>
         </is>
       </c>
     </row>
@@ -10899,12 +10899,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -10952,12 +10952,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11058,12 +11058,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11111,12 +11111,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11164,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11217,12 +11217,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11323,12 +11323,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11376,12 +11376,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11429,12 +11429,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11482,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11588,12 +11588,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11641,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11694,12 +11694,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11747,12 +11747,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11800,12 +11800,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11853,12 +11853,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11906,12 +11906,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -11959,12 +11959,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12065,12 +12065,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12118,12 +12118,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12171,12 +12171,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12224,12 +12224,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12277,12 +12277,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12330,12 +12330,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12383,12 +12383,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12436,12 +12436,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12489,12 +12489,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12542,12 +12542,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12595,12 +12595,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12648,12 +12648,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12701,12 +12701,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12754,12 +12754,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12860,12 +12860,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12913,12 +12913,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -12966,12 +12966,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13019,12 +13019,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13076,12 +13076,12 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>15 days, 16:39:14.432844</t>
+          <t>14 days, 16:20:18.427129</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>15 days, 16:39:14.432809</t>
+          <t>14 days, 16:20:18.427093</t>
         </is>
       </c>
     </row>
@@ -13186,12 +13186,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13243,12 +13243,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>15 days, 16:39:14.432747</t>
+          <t>14 days, 16:20:18.427031</t>
         </is>
       </c>
     </row>
@@ -13296,12 +13296,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13349,12 +13349,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13518,12 +13518,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13571,12 +13571,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13624,12 +13624,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13677,12 +13677,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13730,12 +13730,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13783,12 +13783,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13889,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13942,12 +13942,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -13995,12 +13995,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14048,12 +14048,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14101,12 +14101,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14154,12 +14154,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14207,12 +14207,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14260,12 +14260,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14313,12 +14313,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14366,12 +14366,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14419,12 +14419,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14472,12 +14472,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14525,12 +14525,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14578,12 +14578,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14631,12 +14631,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14684,12 +14684,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14737,12 +14737,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14790,12 +14790,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>12 days, 18:24:14.431879</t>
+          <t>11 days, 18:05:18.426147</t>
         </is>
       </c>
     </row>
@@ -14900,12 +14900,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>12 days, 18:24:14.431790</t>
+          <t>11 days, 18:05:18.426065</t>
         </is>
       </c>
     </row>
@@ -15010,12 +15010,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15063,12 +15063,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15116,12 +15116,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15169,12 +15169,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15222,12 +15222,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15275,12 +15275,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15328,12 +15328,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15381,12 +15381,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15434,12 +15434,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15487,12 +15487,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15540,12 +15540,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15593,12 +15593,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15646,12 +15646,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15699,12 +15699,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15805,12 +15805,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15858,12 +15858,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15911,12 +15911,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -15964,12 +15964,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16017,12 +16017,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16070,12 +16070,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16123,12 +16123,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16176,12 +16176,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16282,12 +16282,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16335,12 +16335,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16388,12 +16388,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16441,12 +16441,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16494,12 +16494,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16547,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16600,12 +16600,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16658,12 +16658,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16716,12 +16716,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16774,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16832,12 +16832,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -16948,12 +16948,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17006,12 +17006,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17064,12 +17064,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17122,12 +17122,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17180,12 +17180,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17238,12 +17238,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17296,12 +17296,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17354,12 +17354,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17412,12 +17412,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17470,12 +17470,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17528,12 +17528,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17586,12 +17586,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17639,12 +17639,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17697,12 +17697,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17755,12 +17755,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17813,12 +17813,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17871,12 +17871,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17929,12 +17929,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -17987,12 +17987,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18045,12 +18045,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18103,12 +18103,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18161,12 +18161,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18219,12 +18219,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18277,12 +18277,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18335,12 +18335,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18393,12 +18393,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18451,12 +18451,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18509,12 +18509,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18567,12 +18567,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18625,12 +18625,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18678,12 +18678,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18731,12 +18731,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18784,12 +18784,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>10 days, 0:39:14.429434</t>
+          <t>9 days, 0:20:18.423718</t>
         </is>
       </c>
     </row>
@@ -18837,12 +18837,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18890,12 +18890,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18943,12 +18943,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -18996,12 +18996,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19102,12 +19102,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19155,12 +19155,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19208,12 +19208,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19261,12 +19261,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19314,12 +19314,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19367,12 +19367,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19420,12 +19420,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19473,12 +19473,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19526,12 +19526,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19579,12 +19579,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19632,12 +19632,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19685,12 +19685,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19738,12 +19738,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19791,12 +19791,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19844,12 +19844,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19897,12 +19897,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -19950,12 +19950,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20003,12 +20003,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20056,12 +20056,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20109,12 +20109,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20162,12 +20162,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20215,12 +20215,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20268,12 +20268,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20321,12 +20321,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20374,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20427,12 +20427,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20480,12 +20480,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20533,12 +20533,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20586,12 +20586,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20639,12 +20639,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20692,12 +20692,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20745,12 +20745,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20798,12 +20798,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20851,12 +20851,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20904,12 +20904,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -20957,12 +20957,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21010,12 +21010,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21063,12 +21063,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21116,12 +21116,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21169,12 +21169,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21222,12 +21222,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21275,12 +21275,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21328,12 +21328,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21381,12 +21381,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21434,12 +21434,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21487,12 +21487,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21540,12 +21540,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21593,12 +21593,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21646,12 +21646,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21699,12 +21699,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21752,12 +21752,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21805,12 +21805,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21858,12 +21858,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -21964,12 +21964,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22017,12 +22017,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22070,12 +22070,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22123,12 +22123,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22176,12 +22176,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22229,12 +22229,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22282,12 +22282,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22335,12 +22335,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22388,12 +22388,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22441,12 +22441,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22494,12 +22494,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22547,12 +22547,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22600,12 +22600,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22653,12 +22653,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22706,12 +22706,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22759,12 +22759,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22812,12 +22812,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22865,12 +22865,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22918,12 +22918,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -22971,12 +22971,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23024,12 +23024,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23077,12 +23077,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23130,12 +23130,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23183,12 +23183,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23241,12 +23241,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23299,12 +23299,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23357,12 +23357,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23415,12 +23415,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23468,12 +23468,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23521,12 +23521,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23579,12 +23579,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23637,12 +23637,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23695,12 +23695,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23753,12 +23753,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23811,12 +23811,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23869,12 +23869,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23927,12 +23927,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -23980,12 +23980,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24037,12 +24037,12 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>1 day, 19:39:14.426630</t>
+          <t>19:20:18.420824</t>
         </is>
       </c>
     </row>
@@ -24090,12 +24090,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24148,12 +24148,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24206,12 +24206,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24264,12 +24264,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24322,12 +24322,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24438,12 +24438,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24496,12 +24496,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24554,12 +24554,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24612,12 +24612,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24670,12 +24670,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24728,12 +24728,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24786,12 +24786,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24844,12 +24844,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24902,12 +24902,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -24960,12 +24960,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25018,12 +25018,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25076,12 +25076,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25134,12 +25134,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25192,12 +25192,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25250,12 +25250,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25308,12 +25308,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25366,12 +25366,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25424,12 +25424,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25482,12 +25482,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25540,12 +25540,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25598,12 +25598,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25656,12 +25656,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25714,12 +25714,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25772,12 +25772,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25830,12 +25830,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25888,12 +25888,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -25946,12 +25946,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -26004,12 +26004,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>
@@ -26062,12 +26062,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>09/18/26 02:20 PM</t>
+          <t>09/19/26 02:39 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,17 +546,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403491</t>
+          <t>22 days, 0:10:22.098130</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403430</t>
+          <t>22 days, 0:10:22.098071</t>
         </is>
       </c>
     </row>
@@ -670,17 +670,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403388</t>
+          <t>22 days, 0:10:22.098029</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403351</t>
+          <t>22 days, 0:10:22.097993</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403315</t>
+          <t>22 days, 0:10:22.097958</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403280</t>
+          <t>22 days, 0:10:22.097925</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403245</t>
+          <t>22 days, 0:10:22.097892</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403211</t>
+          <t>22 days, 0:10:22.097860</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403177</t>
+          <t>22 days, 0:10:22.097828</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403141</t>
+          <t>22 days, 0:10:22.097794</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1166,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403107</t>
+          <t>22 days, 0:10:22.097761</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403073</t>
+          <t>22 days, 0:10:22.097730</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.403037</t>
+          <t>22 days, 0:10:22.097696</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.402981</t>
+          <t>22 days, 0:10:22.097662</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.402939</t>
+          <t>22 days, 0:10:22.097629</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23 days, 1:09:39.402905</t>
+          <t>22 days, 0:10:22.097596</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,19 +1584,15 @@
           <t>10/19/26 03:00 pm</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>VDC &amp; WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>22 days, 23:54:39.402812</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1644,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402770</t>
+          <t>21 days, 21:55:22.097468</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1701,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402729</t>
+          <t>21 days, 21:55:22.097426</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1758,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402691</t>
+          <t>21 days, 21:55:22.097359</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1815,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402652</t>
+          <t>21 days, 21:55:22.097314</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402613</t>
+          <t>21 days, 21:55:22.097274</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1929,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402574</t>
+          <t>21 days, 21:55:22.097234</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1986,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402531</t>
+          <t>21 days, 21:55:22.097199</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2043,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402494</t>
+          <t>21 days, 21:55:22.097166</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2100,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402457</t>
+          <t>21 days, 21:55:22.097131</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2157,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402421</t>
+          <t>21 days, 21:55:22.097098</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2214,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402385</t>
+          <t>21 days, 21:55:22.097064</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2271,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22 days, 22:54:39.402351</t>
+          <t>21 days, 21:55:22.097029</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2328,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402314</t>
+          <t>21 days, 21:10:22.096994</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2385,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402277</t>
+          <t>21 days, 21:10:22.096959</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2442,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402241</t>
+          <t>21 days, 21:10:22.096924</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2499,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402202</t>
+          <t>21 days, 21:10:22.096889</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2556,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402167</t>
+          <t>21 days, 21:10:22.096853</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2613,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402129</t>
+          <t>21 days, 21:10:22.096818</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2670,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402091</t>
+          <t>21 days, 21:10:22.096780</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2727,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402054</t>
+          <t>21 days, 21:10:22.096746</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2784,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.402017</t>
+          <t>21 days, 21:10:22.096711</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2841,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401958</t>
+          <t>21 days, 21:10:22.096675</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2898,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401918</t>
+          <t>21 days, 21:10:22.096640</t>
         </is>
       </c>
     </row>
@@ -2959,12 +2955,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401881</t>
+          <t>21 days, 21:10:22.096607</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3012,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401847</t>
+          <t>21 days, 21:10:22.096574</t>
         </is>
       </c>
     </row>
@@ -3073,12 +3069,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401811</t>
+          <t>21 days, 21:10:22.096540</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3126,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401773</t>
+          <t>21 days, 21:10:22.096503</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3183,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401738</t>
+          <t>21 days, 21:10:22.096470</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3240,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401701</t>
+          <t>21 days, 21:10:22.096434</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3297,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401662</t>
+          <t>21 days, 21:10:22.096382</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3354,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401627</t>
+          <t>21 days, 21:10:22.096342</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3411,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401593</t>
+          <t>21 days, 21:10:22.096308</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3468,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401558</t>
+          <t>21 days, 21:10:22.096273</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3525,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401526</t>
+          <t>21 days, 21:10:22.096241</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3582,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401494</t>
+          <t>21 days, 21:10:22.096209</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3639,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>22 days, 22:09:39.401461</t>
+          <t>21 days, 21:10:22.096176</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3696,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401426</t>
+          <t>21 days, 20:10:22.096141</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3753,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401393</t>
+          <t>21 days, 20:10:22.096105</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3810,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401358</t>
+          <t>21 days, 20:10:22.096070</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3867,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401323</t>
+          <t>21 days, 20:10:22.096035</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3924,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401289</t>
+          <t>21 days, 20:10:22.096001</t>
         </is>
       </c>
     </row>
@@ -3985,12 +3981,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401255</t>
+          <t>21 days, 20:10:22.095967</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4038,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401221</t>
+          <t>21 days, 20:10:22.095933</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4095,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401188</t>
+          <t>21 days, 20:10:22.095899</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4152,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401155</t>
+          <t>21 days, 20:10:22.095867</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4209,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401120</t>
+          <t>21 days, 20:10:22.095835</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4266,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401086</t>
+          <t>21 days, 20:10:22.095803</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4323,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401049</t>
+          <t>21 days, 20:10:22.095770</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4380,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.401013</t>
+          <t>21 days, 20:10:22.095736</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4437,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.400954</t>
+          <t>21 days, 20:10:22.095703</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4494,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>22 days, 21:09:39.400916</t>
+          <t>21 days, 20:10:22.095670</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4551,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400877</t>
+          <t>21 days, 18:40:22.095634</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4608,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400839</t>
+          <t>21 days, 18:40:22.095599</t>
         </is>
       </c>
     </row>
@@ -4669,12 +4665,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400805</t>
+          <t>21 days, 18:40:22.095567</t>
         </is>
       </c>
     </row>
@@ -4721,17 +4717,17 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400772</t>
+          <t>21 days, 18:40:22.095534</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4779,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400738</t>
+          <t>21 days, 18:40:22.095500</t>
         </is>
       </c>
     </row>
@@ -4835,17 +4831,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400698</t>
+          <t>21 days, 18:40:22.095463</t>
         </is>
       </c>
     </row>
@@ -4892,17 +4888,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400664</t>
+          <t>21 days, 18:40:22.095430</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4945,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400627</t>
+          <t>21 days, 18:40:22.095374</t>
         </is>
       </c>
     </row>
@@ -5006,17 +5002,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC &amp; WASA02 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400589</t>
+          <t>21 days, 18:40:22.095332</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5059,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC &amp; WASA02 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400551</t>
+          <t>21 days, 18:40:22.095294</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5121,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400515</t>
+          <t>21 days, 18:40:22.095259</t>
         </is>
       </c>
     </row>
@@ -5177,17 +5173,17 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400479</t>
+          <t>21 days, 18:40:22.095227</t>
         </is>
       </c>
     </row>
@@ -5234,17 +5230,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400444</t>
+          <t>21 days, 18:40:22.095193</t>
         </is>
       </c>
     </row>
@@ -5291,17 +5287,17 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400410</t>
+          <t>21 days, 18:40:22.095161</t>
         </is>
       </c>
     </row>
@@ -5348,17 +5344,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400376</t>
+          <t>21 days, 18:40:22.095128</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5406,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400343</t>
+          <t>21 days, 18:40:22.095094</t>
         </is>
       </c>
     </row>
@@ -5467,12 +5463,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400310</t>
+          <t>21 days, 18:40:22.095062</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5520,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400278</t>
+          <t>21 days, 18:40:22.095029</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5577,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400245</t>
+          <t>21 days, 18:40:22.094995</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5634,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400213</t>
+          <t>21 days, 18:40:22.094962</t>
         </is>
       </c>
     </row>
@@ -5695,12 +5691,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400181</t>
+          <t>21 days, 18:40:22.094930</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5748,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>22 days, 19:39:39.400149</t>
+          <t>21 days, 18:40:22.094897</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5805,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.400115</t>
+          <t>21 days, 17:55:22.094862</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5862,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.400081</t>
+          <t>21 days, 17:55:22.094828</t>
         </is>
       </c>
     </row>
@@ -5923,12 +5919,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.400046</t>
+          <t>21 days, 17:55:22.094794</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5976,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.400012</t>
+          <t>21 days, 17:55:22.094761</t>
         </is>
       </c>
     </row>
@@ -6037,12 +6033,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.399944</t>
+          <t>21 days, 17:55:22.094728</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6090,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.399904</t>
+          <t>21 days, 17:55:22.094696</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6147,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>22 days, 18:54:39.399869</t>
+          <t>21 days, 17:55:22.094663</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6204,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399833</t>
+          <t>21 days, 17:40:22.094628</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6261,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399798</t>
+          <t>21 days, 17:40:22.094595</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6318,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399763</t>
+          <t>21 days, 17:40:22.094561</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6375,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399728</t>
+          <t>21 days, 17:40:22.094527</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6432,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399693</t>
+          <t>21 days, 17:40:22.094493</t>
         </is>
       </c>
     </row>
@@ -6493,12 +6489,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>22 days, 18:39:39.399659</t>
+          <t>21 days, 17:40:22.094458</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6546,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>22 days, 18:24:39.399626</t>
+          <t>21 days, 17:25:22.094427</t>
         </is>
       </c>
     </row>
@@ -6607,12 +6603,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>22 days, 18:24:39.399594</t>
+          <t>21 days, 17:25:22.094370</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6660,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>22 days, 18:24:39.399561</t>
+          <t>21 days, 17:25:22.094330</t>
         </is>
       </c>
     </row>
@@ -6721,12 +6717,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>22 days, 18:24:39.399528</t>
+          <t>21 days, 17:25:22.094295</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6774,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399491</t>
+          <t>21 days, 17:10:22.094257</t>
         </is>
       </c>
     </row>
@@ -6835,12 +6831,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399454</t>
+          <t>21 days, 17:10:22.094220</t>
         </is>
       </c>
     </row>
@@ -6892,12 +6888,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399417</t>
+          <t>21 days, 17:10:22.094184</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6945,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399381</t>
+          <t>21 days, 17:10:22.094148</t>
         </is>
       </c>
     </row>
@@ -7006,12 +7002,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399345</t>
+          <t>21 days, 17:10:22.094113</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7059,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399310</t>
+          <t>21 days, 17:10:22.094077</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7116,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>22 days, 18:09:39.399273</t>
+          <t>21 days, 17:10:22.094043</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7169,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7222,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7279,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.399164</t>
+          <t>21 days, 16:25:22.093938</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7336,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.399129</t>
+          <t>21 days, 16:25:22.093903</t>
         </is>
       </c>
     </row>
@@ -7397,12 +7393,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.399097</t>
+          <t>21 days, 16:25:22.093871</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7450,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.399066</t>
+          <t>21 days, 16:25:22.093840</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7507,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.399032</t>
+          <t>21 days, 16:25:22.093805</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7564,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.398969</t>
+          <t>21 days, 16:25:22.093773</t>
         </is>
       </c>
     </row>
@@ -7621,12 +7617,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -7678,12 +7674,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.398891</t>
+          <t>21 days, 16:25:22.093704</t>
         </is>
       </c>
     </row>
@@ -7735,12 +7731,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.398855</t>
+          <t>21 days, 16:25:22.093670</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7788,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.398822</t>
+          <t>21 days, 16:25:22.093636</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7845,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>22 days, 17:24:39.398789</t>
+          <t>21 days, 16:25:22.093604</t>
         </is>
       </c>
     </row>
@@ -7906,12 +7902,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398755</t>
+          <t>21 days, 16:10:22.093573</t>
         </is>
       </c>
     </row>
@@ -7963,12 +7959,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398721</t>
+          <t>21 days, 16:10:22.093539</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8016,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398689</t>
+          <t>21 days, 16:10:22.093507</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8073,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398656</t>
+          <t>21 days, 16:10:22.093476</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8130,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398625</t>
+          <t>21 days, 16:10:22.093444</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8187,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398594</t>
+          <t>21 days, 16:10:22.093414</t>
         </is>
       </c>
     </row>
@@ -8248,12 +8244,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398563</t>
+          <t>21 days, 16:10:22.093356</t>
         </is>
       </c>
     </row>
@@ -8305,12 +8301,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398529</t>
+          <t>21 days, 16:10:22.093320</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8358,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398497</t>
+          <t>21 days, 16:10:22.093288</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8415,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>22 days, 17:09:39.398459</t>
+          <t>21 days, 16:10:22.093257</t>
         </is>
       </c>
     </row>
@@ -8472,12 +8468,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -8529,12 +8525,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398386</t>
+          <t>18 days, 16:25:22.093188</t>
         </is>
       </c>
     </row>
@@ -8586,12 +8582,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398349</t>
+          <t>18 days, 16:25:22.093151</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8639,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398314</t>
+          <t>18 days, 16:25:22.093115</t>
         </is>
       </c>
     </row>
@@ -8700,12 +8696,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398278</t>
+          <t>18 days, 16:25:22.093080</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8753,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398242</t>
+          <t>18 days, 16:25:22.093045</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8810,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398206</t>
+          <t>18 days, 16:25:22.093010</t>
         </is>
       </c>
     </row>
@@ -8871,12 +8867,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398170</t>
+          <t>18 days, 16:25:22.092976</t>
         </is>
       </c>
     </row>
@@ -8928,12 +8924,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398135</t>
+          <t>18 days, 16:25:22.092941</t>
         </is>
       </c>
     </row>
@@ -8985,12 +8981,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398099</t>
+          <t>18 days, 16:25:22.092907</t>
         </is>
       </c>
     </row>
@@ -9042,12 +9038,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398064</t>
+          <t>18 days, 16:25:22.092872</t>
         </is>
       </c>
     </row>
@@ -9099,12 +9095,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.398028</t>
+          <t>18 days, 16:25:22.092837</t>
         </is>
       </c>
     </row>
@@ -9156,12 +9152,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.397969</t>
+          <t>18 days, 16:25:22.092804</t>
         </is>
       </c>
     </row>
@@ -9213,12 +9209,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>19 days, 17:24:39.397930</t>
+          <t>18 days, 16:25:22.092769</t>
         </is>
       </c>
     </row>
@@ -9266,12 +9262,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -9319,12 +9315,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9372,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397819</t>
+          <t>17 days, 20:25:22.092665</t>
         </is>
       </c>
     </row>
@@ -9433,12 +9429,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397785</t>
+          <t>17 days, 20:25:22.092630</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9486,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397752</t>
+          <t>17 days, 20:25:22.092597</t>
         </is>
       </c>
     </row>
@@ -9547,12 +9543,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397719</t>
+          <t>17 days, 20:25:22.092564</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9600,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397686</t>
+          <t>17 days, 20:25:22.092532</t>
         </is>
       </c>
     </row>
@@ -9661,12 +9657,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397655</t>
+          <t>17 days, 20:25:22.092501</t>
         </is>
       </c>
     </row>
@@ -9718,12 +9714,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397624</t>
+          <t>17 days, 20:25:22.092469</t>
         </is>
       </c>
     </row>
@@ -9775,12 +9771,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397590</t>
+          <t>17 days, 20:25:22.092434</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9828,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397559</t>
+          <t>17 days, 20:25:22.092389</t>
         </is>
       </c>
     </row>
@@ -9889,12 +9885,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397525</t>
+          <t>17 days, 20:25:22.092347</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9942,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>18 days, 21:24:39.397492</t>
+          <t>17 days, 20:25:22.092311</t>
         </is>
       </c>
     </row>
@@ -10003,12 +9999,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.397461</t>
+          <t>17 days, 20:10:22.092280</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10056,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.397428</t>
+          <t>17 days, 20:10:22.092247</t>
         </is>
       </c>
     </row>
@@ -10117,12 +10113,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.397394</t>
+          <t>17 days, 20:10:22.092212</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10140,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10167,19 +10163,15 @@
           <t>10/15/26 12:15 pm</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>VDC &amp; WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>18 days, 21:09:39.397361</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10193,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10224,19 +10216,15 @@
           <t>10/15/26 12:15 pm</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>18 days, 21:09:39.397328</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10272,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10299,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10334,19 +10322,15 @@
           <t>10/15/26 12:15 pm</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>18 days, 21:09:39.397266</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10378,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10447,12 +10431,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10484,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10553,12 +10537,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10590,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10643,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10696,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10765,12 +10749,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10822,12 +10806,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.396988</t>
+          <t>17 days, 20:10:22.091847</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10859,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10928,12 +10912,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10969,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.396883</t>
+          <t>17 days, 20:10:22.091753</t>
         </is>
       </c>
     </row>
@@ -11038,12 +11022,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11095,12 +11079,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>18 days, 21:09:39.396818</t>
+          <t>17 days, 20:10:22.091690</t>
         </is>
       </c>
     </row>
@@ -11148,12 +11132,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11206,12 +11190,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11264,12 +11248,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11322,12 +11306,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11364,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11438,12 +11422,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11496,12 +11480,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11549,12 +11533,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11591,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11665,12 +11649,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11723,12 +11707,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11765,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11839,12 +11823,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11881,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -11955,12 +11939,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12012,12 +11996,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>17 days, 22:39:39.396360</t>
+          <t>16 days, 21:40:22.091223</t>
         </is>
       </c>
     </row>
@@ -12065,12 +12049,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12118,12 +12102,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12171,12 +12155,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12224,12 +12208,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12277,12 +12261,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12330,12 +12314,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12383,12 +12367,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12436,12 +12420,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12489,12 +12473,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12547,12 +12531,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12600,12 +12584,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12653,12 +12637,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12706,12 +12690,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12759,12 +12743,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12812,12 +12796,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12865,12 +12849,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12918,12 +12902,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -12971,12 +12955,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13024,12 +13008,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13077,12 +13061,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13123,12 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>12 days, 21:39:39.395717</t>
+          <t>11 days, 20:40:22.090626</t>
         </is>
       </c>
     </row>
@@ -13192,12 +13176,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13250,12 +13234,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13308,12 +13292,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13350,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13415,12 +13399,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13468,12 +13452,12 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>12 days, 20:54:39.395533</t>
+          <t>11 days, 19:55:22.090450</t>
         </is>
       </c>
     </row>
@@ -13521,12 +13505,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13578,12 +13562,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>12 days, 18:39:39.395472</t>
+          <t>11 days, 17:40:22.090364</t>
         </is>
       </c>
     </row>
@@ -13631,12 +13615,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13684,12 +13668,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13742,12 +13726,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13800,12 +13784,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13858,12 +13842,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13911,12 +13895,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -13964,12 +13948,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14017,12 +14001,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14070,12 +14054,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14123,12 +14107,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14176,12 +14160,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14229,12 +14213,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14282,12 +14266,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14335,12 +14319,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14372,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14441,12 +14425,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14499,12 +14483,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14561,12 +14545,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>9 days, 20:09:39.394894</t>
+          <t>8 days, 19:10:22.089831</t>
         </is>
       </c>
     </row>
@@ -14623,12 +14607,12 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>9 days, 20:09:39.394853</t>
+          <t>8 days, 19:10:22.089791</t>
         </is>
       </c>
     </row>
@@ -14685,12 +14669,12 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>9 days, 20:09:39.394817</t>
+          <t>8 days, 19:10:22.089756</t>
         </is>
       </c>
     </row>
@@ -14747,12 +14731,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>9 days, 20:09:39.394774</t>
+          <t>8 days, 19:10:22.089716</t>
         </is>
       </c>
     </row>
@@ -14809,12 +14793,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>9 days, 20:09:39.394737</t>
+          <t>8 days, 19:10:22.089682</t>
         </is>
       </c>
     </row>
@@ -14862,12 +14846,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14915,12 +14899,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -14968,12 +14952,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15021,12 +15005,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15074,12 +15058,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15127,12 +15111,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15164,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15233,12 +15217,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15286,12 +15270,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15339,12 +15323,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15392,12 +15376,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15445,12 +15429,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15498,12 +15482,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15551,12 +15535,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15604,12 +15588,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15657,12 +15641,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15710,12 +15694,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15763,12 +15747,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15816,12 +15800,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15853,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15922,12 +15906,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -15975,12 +15959,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16028,12 +16012,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16081,12 +16065,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16134,12 +16118,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16187,12 +16171,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16240,12 +16224,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16293,12 +16277,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16350,12 +16334,12 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>9 days, 17:54:39.393915</t>
+          <t>8 days, 16:55:22.088850</t>
         </is>
       </c>
     </row>
@@ -16403,12 +16387,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16456,12 +16440,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16509,12 +16493,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16546,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16615,12 +16599,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16668,12 +16652,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16721,12 +16705,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16758,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16827,12 +16811,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16880,12 +16864,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16933,12 +16917,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -16986,12 +16970,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17039,12 +17023,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17092,12 +17076,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17145,12 +17129,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17198,12 +17182,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17251,12 +17235,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17304,12 +17288,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17357,12 +17341,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17410,12 +17394,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17447,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17516,12 +17500,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17569,12 +17553,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17611,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17680,12 +17664,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17733,12 +17717,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17790,12 +17774,12 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>9 days, 0:39:39.393135</t>
+          <t>7 days, 23:40:22.088063</t>
         </is>
       </c>
     </row>
@@ -17848,12 +17832,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17901,12 +17885,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -17954,12 +17938,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18012,12 +17996,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18070,12 +18054,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18128,12 +18112,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18186,12 +18170,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18244,12 +18228,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18302,12 +18286,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18360,12 +18344,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18418,12 +18402,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18476,12 +18460,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18534,12 +18518,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18592,12 +18576,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18650,12 +18634,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18708,12 +18692,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18766,12 +18750,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18824,12 +18808,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18882,12 +18866,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18940,12 +18924,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -18998,12 +18982,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19056,12 +19040,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19114,12 +19098,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19172,12 +19156,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19230,12 +19214,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19288,12 +19272,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19346,12 +19330,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19404,12 +19388,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19462,12 +19446,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19504,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19578,12 +19562,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19636,12 +19620,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19694,12 +19678,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19752,12 +19736,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19810,12 +19794,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19868,12 +19852,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19926,12 +19910,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -19984,12 +19968,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20042,12 +20026,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20100,12 +20084,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20158,12 +20142,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20216,12 +20200,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20274,12 +20258,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20332,12 +20316,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20390,12 +20374,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20448,12 +20432,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20506,12 +20490,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20564,12 +20548,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20622,12 +20606,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20680,12 +20664,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20738,12 +20722,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20796,12 +20780,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -20858,12 +20842,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391592</t>
+          <t>7 days, 19:25:22.086604</t>
         </is>
       </c>
     </row>
@@ -20920,12 +20904,12 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391548</t>
+          <t>7 days, 19:25:22.086561</t>
         </is>
       </c>
     </row>
@@ -20982,12 +20966,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391509</t>
+          <t>7 days, 19:25:22.086523</t>
         </is>
       </c>
     </row>
@@ -21044,12 +21028,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391472</t>
+          <t>7 days, 19:25:22.086488</t>
         </is>
       </c>
     </row>
@@ -21106,12 +21090,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391431</t>
+          <t>7 days, 19:25:22.086448</t>
         </is>
       </c>
     </row>
@@ -21168,12 +21152,12 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391393</t>
+          <t>7 days, 19:25:22.086412</t>
         </is>
       </c>
     </row>
@@ -21230,12 +21214,12 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391354</t>
+          <t>7 days, 19:25:22.086355</t>
         </is>
       </c>
     </row>
@@ -21292,12 +21276,12 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391319</t>
+          <t>7 days, 19:25:22.086316</t>
         </is>
       </c>
     </row>
@@ -21354,12 +21338,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391280</t>
+          <t>7 days, 19:25:22.086276</t>
         </is>
       </c>
     </row>
@@ -21416,12 +21400,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391244</t>
+          <t>7 days, 19:25:22.086241</t>
         </is>
       </c>
     </row>
@@ -21478,12 +21462,12 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391206</t>
+          <t>7 days, 19:25:22.086204</t>
         </is>
       </c>
     </row>
@@ -21540,12 +21524,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391168</t>
+          <t>7 days, 19:25:22.086167</t>
         </is>
       </c>
     </row>
@@ -21602,12 +21586,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391128</t>
+          <t>7 days, 19:25:22.086128</t>
         </is>
       </c>
     </row>
@@ -21664,12 +21648,12 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391086</t>
+          <t>7 days, 19:25:22.086086</t>
         </is>
       </c>
     </row>
@@ -21726,12 +21710,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>8 days, 20:24:39.391046</t>
+          <t>7 days, 19:25:22.086047</t>
         </is>
       </c>
     </row>
@@ -21779,12 +21763,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -21832,12 +21816,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -21885,12 +21869,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -21938,12 +21922,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -21991,12 +21975,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22044,12 +22028,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22097,12 +22081,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22150,12 +22134,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22203,12 +22187,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22260,12 +22244,12 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>8 days, 18:24:39.390722</t>
+          <t>7 days, 17:25:22.085768</t>
         </is>
       </c>
     </row>
@@ -22313,12 +22297,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22366,12 +22350,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22419,12 +22403,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22472,12 +22456,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22525,12 +22509,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22578,12 +22562,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22615,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22684,12 +22668,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22737,12 +22721,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22790,12 +22774,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22843,12 +22827,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22896,12 +22880,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -22949,12 +22933,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23002,12 +22986,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23055,12 +23039,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23108,12 +23092,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23161,12 +23145,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23214,12 +23198,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23267,12 +23251,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23320,12 +23304,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23373,12 +23357,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23426,12 +23410,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23479,12 +23463,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23532,12 +23516,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23585,12 +23569,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23638,12 +23622,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23691,12 +23675,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23744,12 +23728,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23797,12 +23781,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23850,12 +23834,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23903,12 +23887,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -23956,12 +23940,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24009,12 +23993,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24062,12 +24046,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24115,12 +24099,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24168,12 +24152,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24205,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24274,12 +24258,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24327,12 +24311,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24364,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24433,12 +24417,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24486,12 +24470,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24539,12 +24523,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24592,12 +24576,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24645,12 +24629,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24682,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24751,12 +24735,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24804,12 +24788,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24857,12 +24841,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24910,12 +24894,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -24963,12 +24947,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25016,12 +25000,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25069,12 +25053,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25122,12 +25106,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25175,12 +25159,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25233,12 +25217,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25286,12 +25270,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25339,12 +25323,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25392,12 +25376,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25445,12 +25429,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25498,12 +25482,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25551,12 +25535,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25604,12 +25588,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25657,12 +25641,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25710,12 +25694,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25763,12 +25747,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25816,12 +25800,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25869,12 +25853,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25922,12 +25906,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -25975,12 +25959,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26028,12 +26012,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26065,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26134,12 +26118,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26187,12 +26171,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26240,12 +26224,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26293,12 +26277,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26346,12 +26330,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26399,12 +26383,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26452,12 +26436,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26505,12 +26489,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26558,12 +26542,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26611,12 +26595,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26652,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>5 days, 17:39:39.388252</t>
+          <t>4 days, 16:40:22.083428</t>
         </is>
       </c>
     </row>
@@ -26721,12 +26705,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26778,12 +26762,12 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>5 days, 17:39:39.388167</t>
+          <t>4 days, 16:40:22.083324</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26815,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26884,12 +26868,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26937,12 +26921,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -26990,12 +26974,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27043,12 +27027,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27096,12 +27080,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27149,12 +27133,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27202,12 +27186,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27255,12 +27239,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27308,12 +27292,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27361,12 +27345,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27414,12 +27398,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27467,12 +27451,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27520,12 +27504,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27573,12 +27557,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27626,12 +27610,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27679,12 +27663,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27732,12 +27716,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27785,12 +27769,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27838,12 +27822,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27891,12 +27875,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27944,12 +27928,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -27997,12 +27981,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28050,12 +28034,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28103,12 +28087,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28156,12 +28140,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28209,12 +28193,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28262,12 +28246,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28315,12 +28299,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28368,12 +28352,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28421,12 +28405,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28479,12 +28463,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28537,12 +28521,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28595,12 +28579,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28653,12 +28637,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28711,12 +28695,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28769,12 +28753,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28827,12 +28811,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28885,12 +28869,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -28943,12 +28927,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29001,12 +28985,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29059,12 +29043,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29117,12 +29101,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29175,12 +29159,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29233,12 +29217,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29291,12 +29275,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29349,12 +29333,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29407,12 +29391,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29460,12 +29444,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29518,12 +29502,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29576,12 +29560,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29634,12 +29618,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29692,12 +29676,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29750,12 +29734,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29808,12 +29792,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29866,12 +29850,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29924,12 +29908,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -29982,12 +29966,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30040,12 +30024,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30098,12 +30082,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30156,12 +30140,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30214,12 +30198,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30272,12 +30256,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30330,12 +30314,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30388,12 +30372,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30446,12 +30430,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30499,12 +30483,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30552,12 +30536,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30605,12 +30589,12 @@
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>2 days, 23:54:39.385807</t>
+          <t>1 day, 22:55:22.081138</t>
         </is>
       </c>
     </row>
@@ -30658,12 +30642,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30711,12 +30695,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30764,12 +30748,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30817,12 +30801,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30870,12 +30854,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30923,12 +30907,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -30976,12 +30960,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31029,12 +31013,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31082,12 +31066,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31135,12 +31119,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31188,12 +31172,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31241,12 +31225,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31294,12 +31278,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31347,12 +31331,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31400,12 +31384,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31453,12 +31437,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31506,12 +31490,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31559,12 +31543,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31612,12 +31596,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>
@@ -31665,12 +31649,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>09/25/26 03:05 PM</t>
+          <t>09/26/26 04:04 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22 days, 22:35:44.726433</t>
+          <t>21 days, 22:01:36.066074</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22 days, 22:35:44.726382</t>
+          <t>21 days, 22:01:36.066012</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 days, 22:35:44.726351</t>
+          <t>21 days, 22:01:36.065970</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 days, 22:35:44.726327</t>
+          <t>21 days, 22:01:36.065933</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 days, 21:20:44.726260</t>
+          <t>21 days, 20:46:36.065889</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 days, 15:05:44.726211</t>
+          <t>21 days, 14:31:36.065852</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726183</t>
+          <t>18 days, 23:31:36.065812</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726156</t>
+          <t>18 days, 23:31:36.065773</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726132</t>
+          <t>18 days, 23:31:36.065736</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726107</t>
+          <t>18 days, 23:31:36.065698</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726083</t>
+          <t>18 days, 23:31:36.065662</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20 days, 0:05:44.726059</t>
+          <t>18 days, 23:31:36.065626</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 23:20:44.726035</t>
+          <t>18 days, 22:46:36.065568</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725916</t>
+          <t>18 days, 22:31:36.065398</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725888</t>
+          <t>18 days, 22:31:36.065356</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725862</t>
+          <t>18 days, 22:31:36.065317</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725838</t>
+          <t>18 days, 22:31:36.065281</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725816</t>
+          <t>18 days, 22:31:36.065246</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725791</t>
+          <t>18 days, 22:31:36.065209</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 23:05:44.725768</t>
+          <t>18 days, 22:31:36.065174</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725721</t>
+          <t>18 days, 20:16:36.065103</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725697</t>
+          <t>18 days, 20:16:36.065065</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725672</t>
+          <t>18 days, 20:16:36.065026</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725643</t>
+          <t>18 days, 20:16:36.064983</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725620</t>
+          <t>18 days, 20:16:36.064948</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725596</t>
+          <t>18 days, 20:16:36.064913</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725573</t>
+          <t>18 days, 20:16:36.064877</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725549</t>
+          <t>18 days, 20:16:36.064842</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725525</t>
+          <t>18 days, 20:16:36.064806</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725501</t>
+          <t>18 days, 20:16:36.064769</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725475</t>
+          <t>18 days, 20:16:36.064730</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725452</t>
+          <t>18 days, 20:16:36.064693</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725428</t>
+          <t>18 days, 20:16:36.064658</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 20:50:44.725402</t>
+          <t>18 days, 20:16:36.064620</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725379</t>
+          <t>18 days, 19:46:36.064565</t>
         </is>
       </c>
     </row>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725355</t>
+          <t>18 days, 19:46:36.064524</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725332</t>
+          <t>18 days, 19:46:36.064487</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725310</t>
+          <t>18 days, 19:46:36.064452</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725258</t>
+          <t>18 days, 19:46:36.064420</t>
         </is>
       </c>
     </row>
@@ -3127,17 +3127,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725230</t>
+          <t>18 days, 19:46:36.064386</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725206</t>
+          <t>18 days, 19:46:36.064352</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725182</t>
+          <t>18 days, 19:46:36.064319</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725158</t>
+          <t>18 days, 19:46:36.064283</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725135</t>
+          <t>18 days, 19:46:36.064250</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725113</t>
+          <t>18 days, 19:46:36.064216</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725089</t>
+          <t>18 days, 19:46:36.064182</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725066</t>
+          <t>18 days, 19:46:36.064148</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725045</t>
+          <t>18 days, 19:46:36.064116</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725023</t>
+          <t>18 days, 19:46:36.064085</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.725000</t>
+          <t>18 days, 19:46:36.064051</t>
         </is>
       </c>
     </row>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ATT01, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>ATT01 &amp; PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724975</t>
+          <t>18 days, 19:46:36.064016</t>
         </is>
       </c>
     </row>
@@ -3876,12 +3876,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724953</t>
+          <t>18 days, 19:46:36.063982</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724931</t>
+          <t>18 days, 19:46:36.063948</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4000,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724909</t>
+          <t>18 days, 19:46:36.063913</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724887</t>
+          <t>18 days, 19:46:36.063878</t>
         </is>
       </c>
     </row>
@@ -4119,17 +4119,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724864</t>
+          <t>18 days, 19:46:36.063845</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724842</t>
+          <t>18 days, 19:46:36.063812</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724816</t>
+          <t>18 days, 19:46:36.063776</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724791</t>
+          <t>18 days, 19:46:36.063740</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724768</t>
+          <t>18 days, 19:46:36.063706</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724746</t>
+          <t>18 days, 19:46:36.063672</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724724</t>
+          <t>18 days, 19:46:36.063639</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4558,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724701</t>
+          <t>18 days, 19:46:36.063604</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724678</t>
+          <t>18 days, 19:46:36.063548</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724656</t>
+          <t>18 days, 19:46:36.063511</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724635</t>
+          <t>18 days, 19:46:36.063477</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724614</t>
+          <t>18 days, 19:46:36.063444</t>
         </is>
       </c>
     </row>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724591</t>
+          <t>18 days, 19:46:36.063408</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724569</t>
+          <t>18 days, 19:46:36.063376</t>
         </is>
       </c>
     </row>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724547</t>
+          <t>18 days, 19:46:36.063342</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724525</t>
+          <t>18 days, 19:46:36.063309</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724505</t>
+          <t>18 days, 19:46:36.063278</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724482</t>
+          <t>18 days, 19:46:36.063243</t>
         </is>
       </c>
     </row>
@@ -5240,12 +5240,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724457</t>
+          <t>18 days, 19:46:36.063206</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724432</t>
+          <t>18 days, 19:46:36.063168</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724409</t>
+          <t>18 days, 19:46:36.063133</t>
         </is>
       </c>
     </row>
@@ -5421,17 +5421,17 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ATT01, PEPCODC &amp; WGL07 - Not yet responded</t>
+          <t>ATT01 &amp; PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724386</t>
+          <t>18 days, 19:46:36.063097</t>
         </is>
       </c>
     </row>
@@ -5483,17 +5483,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ATT01, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>ATT01 &amp; PEPCODC - Not yet responded</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724362</t>
+          <t>18 days, 19:46:36.063062</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724339</t>
+          <t>18 days, 19:46:36.063026</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724316</t>
+          <t>18 days, 19:46:36.062990</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724283</t>
+          <t>18 days, 19:46:36.062955</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724255</t>
+          <t>18 days, 19:46:36.062921</t>
         </is>
       </c>
     </row>
@@ -5798,12 +5798,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724232</t>
+          <t>18 days, 19:46:36.062886</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724209</t>
+          <t>18 days, 19:46:36.062852</t>
         </is>
       </c>
     </row>
@@ -5922,12 +5922,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724186</t>
+          <t>18 days, 19:46:36.062817</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>19 days, 20:20:44.724164</t>
+          <t>18 days, 19:46:36.062783</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.724138</t>
+          <t>18 days, 19:31:36.062743</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.724110</t>
+          <t>18 days, 19:31:36.062702</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.724082</t>
+          <t>18 days, 19:31:36.062659</t>
         </is>
       </c>
     </row>
@@ -6232,12 +6232,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.724052</t>
+          <t>18 days, 19:31:36.062618</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.724019</t>
+          <t>18 days, 19:31:36.062545</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723989</t>
+          <t>18 days, 19:31:36.062497</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723963</t>
+          <t>18 days, 19:31:36.062454</t>
         </is>
       </c>
     </row>
@@ -6480,12 +6480,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723933</t>
+          <t>18 days, 19:31:36.062408</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723901</t>
+          <t>18 days, 19:31:36.062354</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723868</t>
+          <t>18 days, 19:31:36.062310</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723839</t>
+          <t>18 days, 19:31:36.062270</t>
         </is>
       </c>
     </row>
@@ -6728,12 +6728,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723814</t>
+          <t>18 days, 19:31:36.062234</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723787</t>
+          <t>18 days, 19:31:36.062193</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723758</t>
+          <t>18 days, 19:31:36.062151</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723730</t>
+          <t>18 days, 19:31:36.062111</t>
         </is>
       </c>
     </row>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723702</t>
+          <t>18 days, 19:31:36.062070</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723673</t>
+          <t>18 days, 19:31:36.062027</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723645</t>
+          <t>18 days, 19:31:36.061985</t>
         </is>
       </c>
     </row>
@@ -7162,12 +7162,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723618</t>
+          <t>18 days, 19:31:36.061944</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723594</t>
+          <t>18 days, 19:31:36.061907</t>
         </is>
       </c>
     </row>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>19 days, 20:05:44.723570</t>
+          <t>18 days, 19:31:36.061872</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723545</t>
+          <t>18 days, 18:01:36.061837</t>
         </is>
       </c>
     </row>
@@ -7396,12 +7396,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723523</t>
+          <t>18 days, 18:01:36.061804</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723501</t>
+          <t>18 days, 18:01:36.061771</t>
         </is>
       </c>
     </row>
@@ -7510,12 +7510,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723479</t>
+          <t>18 days, 18:01:36.061738</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723458</t>
+          <t>18 days, 18:01:36.061706</t>
         </is>
       </c>
     </row>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>19 days, 18:35:44.723438</t>
+          <t>18 days, 18:01:36.061675</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723416</t>
+          <t>18 days, 17:46:36.061642</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723394</t>
+          <t>18 days, 17:46:36.061608</t>
         </is>
       </c>
     </row>
@@ -7813,12 +7813,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723370</t>
+          <t>18 days, 17:46:36.061553</t>
         </is>
       </c>
     </row>
@@ -7876,12 +7876,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723348</t>
+          <t>18 days, 17:46:36.061516</t>
         </is>
       </c>
     </row>
@@ -7939,12 +7939,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723327</t>
+          <t>18 days, 17:46:36.061483</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723283</t>
+          <t>18 days, 17:46:36.061448</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723258</t>
+          <t>18 days, 17:46:36.061416</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723236</t>
+          <t>18 days, 17:46:36.061386</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723213</t>
+          <t>18 days, 17:46:36.061352</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723191</t>
+          <t>18 days, 17:46:36.061320</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723167</t>
+          <t>18 days, 17:46:36.061287</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723145</t>
+          <t>18 days, 17:46:36.061255</t>
         </is>
       </c>
     </row>
@@ -8443,12 +8443,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723119</t>
+          <t>18 days, 17:46:36.061222</t>
         </is>
       </c>
     </row>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723098</t>
+          <t>18 days, 17:46:36.061191</t>
         </is>
       </c>
     </row>
@@ -8569,12 +8569,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723076</t>
+          <t>18 days, 17:46:36.061157</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8632,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723053</t>
+          <t>18 days, 17:46:36.061125</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723033</t>
+          <t>18 days, 17:46:36.061095</t>
         </is>
       </c>
     </row>
@@ -8758,12 +8758,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.723011</t>
+          <t>18 days, 17:46:36.061063</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722990</t>
+          <t>18 days, 17:46:36.061031</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722967</t>
+          <t>18 days, 17:46:36.060997</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722945</t>
+          <t>18 days, 17:46:36.060964</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722925</t>
+          <t>18 days, 17:46:36.060934</t>
         </is>
       </c>
     </row>
@@ -9073,12 +9073,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722905</t>
+          <t>18 days, 17:46:36.060903</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722883</t>
+          <t>18 days, 17:46:36.060872</t>
         </is>
       </c>
     </row>
@@ -9199,12 +9199,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722859</t>
+          <t>18 days, 17:46:36.060837</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722838</t>
+          <t>18 days, 17:46:36.060806</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722816</t>
+          <t>18 days, 17:46:36.060775</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722795</t>
+          <t>18 days, 17:46:36.060743</t>
         </is>
       </c>
     </row>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722772</t>
+          <t>18 days, 17:46:36.060710</t>
         </is>
       </c>
     </row>
@@ -9513,12 +9513,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722750</t>
+          <t>18 days, 17:46:36.060676</t>
         </is>
       </c>
     </row>
@@ -9576,12 +9576,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722729</t>
+          <t>18 days, 17:46:36.060646</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722708</t>
+          <t>18 days, 17:46:36.060614</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722680</t>
+          <t>18 days, 17:46:36.060558</t>
         </is>
       </c>
     </row>
@@ -9763,12 +9763,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722658</t>
+          <t>18 days, 17:46:36.060522</t>
         </is>
       </c>
     </row>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722637</t>
+          <t>18 days, 17:46:36.060492</t>
         </is>
       </c>
     </row>
@@ -9887,12 +9887,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722611</t>
+          <t>18 days, 17:46:36.060454</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722584</t>
+          <t>18 days, 17:46:36.060416</t>
         </is>
       </c>
     </row>
@@ -10011,12 +10011,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722562</t>
+          <t>18 days, 17:46:36.060384</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722537</t>
+          <t>18 days, 17:46:36.060348</t>
         </is>
       </c>
     </row>
@@ -10135,12 +10135,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722511</t>
+          <t>18 days, 17:46:36.060310</t>
         </is>
       </c>
     </row>
@@ -10197,12 +10197,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722483</t>
+          <t>18 days, 17:46:36.060269</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722460</t>
+          <t>18 days, 17:46:36.060236</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722430</t>
+          <t>18 days, 17:46:36.060194</t>
         </is>
       </c>
     </row>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722405</t>
+          <t>18 days, 17:46:36.060157</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722384</t>
+          <t>18 days, 17:46:36.060127</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722364</t>
+          <t>18 days, 17:46:36.060095</t>
         </is>
       </c>
     </row>
@@ -10569,12 +10569,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722343</t>
+          <t>18 days, 17:46:36.060065</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722320</t>
+          <t>18 days, 17:46:36.060030</t>
         </is>
       </c>
     </row>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722276</t>
+          <t>18 days, 17:46:36.059996</t>
         </is>
       </c>
     </row>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722229</t>
+          <t>18 days, 17:46:36.059963</t>
         </is>
       </c>
     </row>
@@ -10817,12 +10817,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722198</t>
+          <t>18 days, 17:46:36.059925</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722170</t>
+          <t>18 days, 17:46:36.059887</t>
         </is>
       </c>
     </row>
@@ -10941,12 +10941,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722141</t>
+          <t>18 days, 17:46:36.059848</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722115</t>
+          <t>18 days, 17:46:36.059812</t>
         </is>
       </c>
     </row>
@@ -11065,12 +11065,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722093</t>
+          <t>18 days, 17:46:36.059780</t>
         </is>
       </c>
     </row>
@@ -11127,12 +11127,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722071</t>
+          <t>18 days, 17:46:36.059749</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722044</t>
+          <t>18 days, 17:46:36.059710</t>
         </is>
       </c>
     </row>
@@ -11251,12 +11251,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.722018</t>
+          <t>18 days, 17:46:36.059670</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721996</t>
+          <t>18 days, 17:46:36.059637</t>
         </is>
       </c>
     </row>
@@ -11375,12 +11375,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721968</t>
+          <t>18 days, 17:46:36.059598</t>
         </is>
       </c>
     </row>
@@ -11437,12 +11437,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721940</t>
+          <t>18 days, 17:46:36.059536</t>
         </is>
       </c>
     </row>
@@ -11499,12 +11499,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721917</t>
+          <t>18 days, 17:46:36.059501</t>
         </is>
       </c>
     </row>
@@ -11561,12 +11561,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721894</t>
+          <t>18 days, 17:46:36.059471</t>
         </is>
       </c>
     </row>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>19 days, 18:20:44.721871</t>
+          <t>18 days, 17:46:36.059439</t>
         </is>
       </c>
     </row>
@@ -11685,12 +11685,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>19 days, 17:20:44.721847</t>
+          <t>18 days, 16:46:36.059403</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11743,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>19 days, 17:20:44.721797</t>
+          <t>18 days, 16:46:36.059326</t>
         </is>
       </c>
     </row>
@@ -11867,12 +11867,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>19 days, 17:20:44.721772</t>
+          <t>18 days, 16:46:36.059290</t>
         </is>
       </c>
     </row>
@@ -11929,12 +11929,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>19 days, 17:20:44.721748</t>
+          <t>18 days, 16:46:36.059254</t>
         </is>
       </c>
     </row>
@@ -11982,12 +11982,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12035,12 +12035,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12088,12 +12088,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12141,12 +12141,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12194,12 +12194,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12247,12 +12247,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12300,12 +12300,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12406,12 +12406,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12463,12 +12463,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>17 days, 21:20:44.721535</t>
+          <t>16 days, 20:46:36.058924</t>
         </is>
       </c>
     </row>
@@ -12516,12 +12516,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12569,12 +12569,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12622,12 +12622,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12728,12 +12728,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12781,12 +12781,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12834,12 +12834,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12887,12 +12887,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12940,12 +12940,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12990,19 +12990,15 @@
           <t>10/21/26 12:45 pm</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>MCI03 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>17 days, 20:50:44.721308</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13050,12 +13046,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13099,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13156,12 +13152,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13209,12 +13205,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13267,12 +13263,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13320,12 +13316,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13374,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13436,12 +13432,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13494,12 +13490,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13552,12 +13548,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13606,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13668,12 +13664,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13726,12 +13722,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13784,12 +13780,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13842,12 +13838,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13900,12 +13896,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -13958,12 +13954,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14016,12 +14012,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14074,12 +14070,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14132,12 +14128,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14190,12 +14186,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14248,12 +14244,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14301,12 +14297,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14354,12 +14350,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14407,12 +14403,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14460,12 +14456,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14513,12 +14509,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14566,12 +14562,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14619,12 +14615,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14672,12 +14668,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14725,12 +14721,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14774,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14831,12 +14827,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14884,12 +14880,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14937,12 +14933,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -14990,12 +14986,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15043,12 +15039,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15096,12 +15092,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15149,12 +15145,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15202,12 +15198,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15255,12 +15251,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15308,12 +15304,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15361,12 +15357,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15414,12 +15410,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15467,12 +15463,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15520,12 +15516,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15573,12 +15569,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15626,12 +15622,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15679,12 +15675,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15732,12 +15728,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15785,12 +15781,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15838,12 +15834,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15891,12 +15887,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15944,12 +15940,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -15997,12 +15993,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16054,12 +16050,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>15 days, 21:20:44.720213</t>
+          <t>14 days, 20:46:36.056887</t>
         </is>
       </c>
     </row>
@@ -16107,12 +16103,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16160,12 +16156,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16213,12 +16209,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16266,12 +16262,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16319,12 +16315,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16372,12 +16368,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16425,12 +16421,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16478,12 +16474,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16531,12 +16527,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16584,12 +16580,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16637,12 +16633,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16690,12 +16686,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16743,12 +16739,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16796,12 +16792,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16849,12 +16845,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16902,12 +16898,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -16955,12 +16951,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17008,12 +17004,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17061,12 +17057,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17114,12 +17110,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17167,12 +17163,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17220,12 +17216,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17273,12 +17269,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17326,12 +17322,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17379,12 +17375,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17432,12 +17428,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17485,12 +17481,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17538,12 +17534,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17587,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17644,12 +17640,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17697,12 +17693,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17750,12 +17746,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17799,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17856,12 +17852,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -17913,12 +17909,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>15 days, 18:50:44.719565</t>
+          <t>14 days, 18:16:36.055888</t>
         </is>
       </c>
     </row>
@@ -17966,12 +17962,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18019,12 +18015,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18072,12 +18068,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18125,12 +18121,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18178,12 +18174,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18231,12 +18227,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18284,12 +18280,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18337,12 +18333,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18390,12 +18386,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18443,12 +18439,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18496,12 +18492,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18549,12 +18545,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18602,12 +18598,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18655,12 +18651,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18708,12 +18704,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18761,12 +18757,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18814,12 +18810,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18867,12 +18863,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18920,12 +18916,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -18973,12 +18969,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19026,12 +19022,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19079,12 +19075,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19132,12 +19128,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19181,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19238,12 +19234,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19291,12 +19287,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19344,12 +19340,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19397,12 +19393,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19450,12 +19446,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19503,12 +19499,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19556,12 +19552,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19609,12 +19605,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19662,12 +19658,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19715,12 +19711,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19768,12 +19764,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19821,12 +19817,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19874,12 +19870,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19927,12 +19923,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -19980,12 +19976,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20033,12 +20029,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20086,12 +20082,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20139,12 +20135,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20192,12 +20188,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20245,12 +20241,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20298,12 +20294,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20347,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20404,12 +20400,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20457,12 +20453,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20510,12 +20506,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20563,12 +20559,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20616,12 +20612,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20669,12 +20665,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20722,12 +20718,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20775,12 +20771,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20832,12 +20828,12 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>12 days, 16:35:44.718477</t>
+          <t>11 days, 16:01:36.054214</t>
         </is>
       </c>
     </row>
@@ -20885,12 +20881,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20938,12 +20934,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -20991,12 +20987,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21044,12 +21040,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21097,12 +21093,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21150,12 +21146,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21203,12 +21199,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21256,12 +21252,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21309,12 +21305,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21362,12 +21358,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21415,12 +21411,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21468,12 +21464,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21517,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21574,12 +21570,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21627,12 +21623,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21680,12 +21676,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21733,12 +21729,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21786,12 +21782,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21839,12 +21835,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21892,12 +21888,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21945,12 +21941,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -21998,12 +21994,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22051,12 +22047,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22100,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22157,12 +22153,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22210,12 +22206,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22263,12 +22259,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22316,12 +22312,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22369,12 +22365,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22422,12 +22418,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22475,12 +22471,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22528,12 +22524,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22581,12 +22577,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22634,12 +22630,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22687,12 +22683,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22740,12 +22736,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22793,12 +22789,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22846,12 +22842,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22899,12 +22895,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -22952,12 +22948,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23005,12 +23001,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23058,12 +23054,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23107,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23164,12 +23160,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23217,12 +23213,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23270,12 +23266,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23323,12 +23319,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23376,12 +23372,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23429,12 +23425,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23482,12 +23478,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23535,12 +23531,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23588,12 +23584,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23641,12 +23637,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23694,12 +23690,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23747,12 +23743,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23800,12 +23796,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23853,12 +23849,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23906,12 +23902,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -23959,12 +23955,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24012,12 +24008,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24065,12 +24061,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24122,12 +24118,12 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>10 days, 21:50:44.717247</t>
+          <t>9 days, 21:16:36.052450</t>
         </is>
       </c>
     </row>
@@ -24175,12 +24171,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24228,12 +24224,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24277,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24334,12 +24330,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24387,12 +24383,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24440,12 +24436,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24493,12 +24489,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24546,12 +24542,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24599,12 +24595,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24652,12 +24648,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24705,12 +24701,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24758,12 +24754,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24811,12 +24807,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24864,12 +24860,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24917,12 +24913,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -24970,12 +24966,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25023,12 +25019,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25076,12 +25072,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25129,12 +25125,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25182,12 +25178,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25244,12 +25240,12 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>5 days, 20:50:44.716826</t>
+          <t>4 days, 20:16:36.051827</t>
         </is>
       </c>
     </row>
@@ -25297,12 +25293,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25350,12 +25346,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25403,12 +25399,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25456,12 +25452,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25505,12 +25501,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25558,12 +25554,12 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>5 days, 20:05:44.716706</t>
+          <t>4 days, 19:31:36.051647</t>
         </is>
       </c>
     </row>
@@ -25611,12 +25607,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25668,12 +25664,12 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>5 days, 17:50:44.716665</t>
+          <t>4 days, 17:16:36.051569</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25717,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25774,12 +25770,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25832,12 +25828,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25885,12 +25881,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25938,12 +25934,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -25991,12 +25987,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26044,12 +26040,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26097,12 +26093,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26150,12 +26146,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26203,12 +26199,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26256,12 +26252,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26309,12 +26305,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26362,12 +26358,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26415,12 +26411,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26468,12 +26464,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26521,12 +26517,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26579,12 +26575,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26637,12 +26633,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26691,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26753,12 +26749,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26815,12 +26811,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>2 days, 19:20:44.716224</t>
+          <t>1 day, 18:46:36.050934</t>
         </is>
       </c>
     </row>
@@ -26873,12 +26869,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26926,12 +26922,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -26979,12 +26975,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27032,12 +27028,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27085,12 +27081,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27138,12 +27134,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27191,12 +27187,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27244,12 +27240,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27297,12 +27293,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27350,12 +27346,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27403,12 +27399,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27456,12 +27452,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27509,12 +27505,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27562,12 +27558,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27615,12 +27611,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27668,12 +27664,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27721,12 +27717,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27774,12 +27770,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27827,12 +27823,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27880,12 +27876,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27933,12 +27929,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -27986,12 +27982,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28039,12 +28035,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28092,12 +28088,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28145,12 +28141,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28198,12 +28194,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28251,12 +28247,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28304,12 +28300,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28357,12 +28353,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28414,12 +28410,12 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>2 days, 17:05:44.715681</t>
+          <t>1 day, 16:31:36.050084</t>
         </is>
       </c>
     </row>
@@ -28467,12 +28463,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28520,12 +28516,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28573,12 +28569,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28626,12 +28622,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28679,12 +28675,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28732,12 +28728,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28785,12 +28781,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28838,12 +28834,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28891,12 +28887,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28944,12 +28940,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -28997,12 +28993,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29050,12 +29046,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29103,12 +29099,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29156,12 +29152,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29209,12 +29205,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29262,12 +29258,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29315,12 +29311,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29368,12 +29364,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29421,12 +29417,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29474,12 +29470,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29527,12 +29523,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29580,12 +29576,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29633,12 +29629,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29686,12 +29682,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29739,12 +29735,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29792,12 +29788,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29849,12 +29845,12 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>1 day, 23:50:44.715148</t>
+          <t>23:16:36.049264</t>
         </is>
       </c>
     </row>
@@ -29902,12 +29898,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -29955,12 +29951,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30008,12 +30004,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30066,12 +30062,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30124,12 +30120,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30182,12 +30178,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30240,12 +30236,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30298,12 +30294,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30356,12 +30352,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30414,12 +30410,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30472,12 +30468,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30530,12 +30526,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30588,12 +30584,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30646,12 +30642,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30704,12 +30700,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30762,12 +30758,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30820,12 +30816,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30878,12 +30874,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30936,12 +30932,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -30994,12 +30990,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31052,12 +31048,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31110,12 +31106,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31168,12 +31164,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31226,12 +31222,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31284,12 +31280,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31342,12 +31338,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31400,12 +31396,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31458,12 +31454,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31516,12 +31512,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31574,12 +31570,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31632,12 +31628,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31690,12 +31686,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31748,12 +31744,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31806,12 +31802,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31864,12 +31860,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31922,12 +31918,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -31980,12 +31976,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32038,12 +32034,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32096,12 +32092,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32154,12 +32150,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32212,12 +32208,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32270,12 +32266,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32328,12 +32324,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32386,12 +32382,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32444,12 +32440,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32502,12 +32498,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32560,12 +32556,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32618,12 +32614,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32676,12 +32672,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32734,12 +32730,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32792,12 +32788,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32850,12 +32846,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32908,12 +32904,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -32966,12 +32962,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33024,12 +33020,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33086,12 +33082,12 @@
       </c>
       <c r="K578" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>1 day, 19:35:44.714092</t>
+          <t>19:01:36.047688</t>
         </is>
       </c>
     </row>
@@ -33144,12 +33140,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33202,12 +33198,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33260,12 +33256,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33322,12 +33318,12 @@
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>1 day, 19:35:44.713994</t>
+          <t>19:01:36.047524</t>
         </is>
       </c>
     </row>
@@ -33384,12 +33380,12 @@
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>1 day, 19:35:44.713966</t>
+          <t>19:01:36.047482</t>
         </is>
       </c>
     </row>
@@ -33442,12 +33438,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33500,12 +33496,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33558,12 +33554,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33616,12 +33612,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33674,12 +33670,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33732,12 +33728,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33785,12 +33781,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33838,12 +33834,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33891,12 +33887,12 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33944,12 +33940,12 @@
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -33997,12 +33993,12 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34050,12 +34046,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34103,12 +34099,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34156,12 +34152,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34209,12 +34205,12 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34266,12 +34262,12 @@
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>1 day, 17:35:44.713626</t>
+          <t>17:01:36.046993</t>
         </is>
       </c>
     </row>
@@ -34319,12 +34315,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34372,12 +34368,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34425,12 +34421,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34478,12 +34474,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34531,12 +34527,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34584,12 +34580,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34637,12 +34633,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34690,12 +34686,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34743,12 +34739,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34796,12 +34792,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34849,12 +34845,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34902,12 +34898,12 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -34955,12 +34951,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35008,12 +35004,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35061,12 +35057,12 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35114,12 +35110,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35167,12 +35163,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35220,12 +35216,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35273,12 +35269,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35326,12 +35322,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35379,12 +35375,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35432,12 +35428,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35485,12 +35481,12 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35538,12 +35534,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35591,12 +35587,12 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35644,12 +35640,12 @@
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35697,12 +35693,12 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35750,12 +35746,12 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35803,12 +35799,12 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35856,12 +35852,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35909,12 +35905,12 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -35962,12 +35958,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36015,12 +36011,12 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36068,12 +36064,12 @@
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36121,12 +36117,12 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36174,12 +36170,12 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36227,12 +36223,12 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36280,12 +36276,12 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36333,12 +36329,12 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36386,12 +36382,12 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36439,12 +36435,12 @@
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36492,12 +36488,12 @@
       <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36545,12 +36541,12 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36598,12 +36594,12 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36651,12 +36647,12 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36704,12 +36700,12 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36757,12 +36753,12 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36810,12 +36806,12 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36863,12 +36859,12 @@
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36916,12 +36912,12 @@
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -36969,12 +36965,12 @@
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -37022,12 +37018,12 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -37075,12 +37071,12 @@
       <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -37128,12 +37124,12 @@
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>
@@ -37181,12 +37177,12 @@
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>10/02/26 03:54 PM</t>
+          <t>10/03/26 04:28 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22 days, 22:28:33.177370</t>
+          <t>21 days, 22:03:04.757284</t>
         </is>
       </c>
     </row>
@@ -608,12 +608,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177320</t>
+          <t>21 days, 21:48:04.757217</t>
         </is>
       </c>
     </row>
@@ -670,12 +670,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177288</t>
+          <t>21 days, 21:48:04.757171</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177259</t>
+          <t>21 days, 21:48:04.757128</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177234</t>
+          <t>21 days, 21:48:04.757090</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177212</t>
+          <t>21 days, 21:48:04.757054</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177189</t>
+          <t>21 days, 21:48:04.757018</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177162</t>
+          <t>21 days, 21:48:04.756977</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177136</t>
+          <t>21 days, 21:48:04.756938</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177112</t>
+          <t>21 days, 21:48:04.756898</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22 days, 22:13:33.177088</t>
+          <t>21 days, 21:48:04.756860</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22 days, 18:13:33.177062</t>
+          <t>21 days, 17:48:04.756823</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22 days, 18:13:33.177040</t>
+          <t>21 days, 17:48:04.756788</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 18:43:33.176912</t>
+          <t>18 days, 18:18:04.756569</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 18:43:33.176889</t>
+          <t>18 days, 18:18:04.756532</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 17:28:33.176844</t>
+          <t>18 days, 17:03:04.756493</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176817</t>
+          <t>18 days, 16:48:04.756455</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176792</t>
+          <t>18 days, 16:48:04.756418</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176768</t>
+          <t>18 days, 16:48:04.756383</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176744</t>
+          <t>18 days, 16:48:04.756346</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176721</t>
+          <t>18 days, 16:48:04.756311</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176698</t>
+          <t>18 days, 16:48:04.756275</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 17:13:33.176674</t>
+          <t>18 days, 16:48:04.756239</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176638</t>
+          <t>18 days, 14:48:04.756202</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176611</t>
+          <t>18 days, 14:48:04.756166</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176586</t>
+          <t>18 days, 14:48:04.756131</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176562</t>
+          <t>18 days, 14:48:04.756093</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176538</t>
+          <t>18 days, 14:48:04.756057</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 15:13:33.176513</t>
+          <t>18 days, 14:48:04.756019</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 14:58:33.176486</t>
+          <t>18 days, 14:33:04.755980</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 14:58:33.176460</t>
+          <t>18 days, 14:33:04.755944</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 14:58:33.176436</t>
+          <t>18 days, 14:33:04.755907</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 14:58:33.176413</t>
+          <t>18 days, 14:33:04.755868</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 14:43:33.176393</t>
+          <t>18 days, 14:18:04.755834</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 14:43:33.176370</t>
+          <t>18 days, 14:18:04.755798</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2784,12 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176301</t>
+          <t>17 days, 22:18:04.755666</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176280</t>
+          <t>17 days, 22:18:04.755626</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176258</t>
+          <t>17 days, 22:18:04.755591</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176237</t>
+          <t>17 days, 22:18:04.755558</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176214</t>
+          <t>17 days, 22:18:04.755522</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176194</t>
+          <t>17 days, 22:18:04.755488</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176173</t>
+          <t>17 days, 22:18:04.755455</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3293,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176152</t>
+          <t>17 days, 22:18:04.755421</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18 days, 22:43:33.176131</t>
+          <t>17 days, 22:18:04.755387</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.176107</t>
+          <t>17 days, 22:03:04.755351</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.176085</t>
+          <t>17 days, 22:03:04.755315</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.176061</t>
+          <t>17 days, 22:03:04.755278</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.176037</t>
+          <t>17 days, 22:03:04.755240</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.176014</t>
+          <t>17 days, 22:03:04.755203</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.175992</t>
+          <t>17 days, 22:03:04.755167</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 22:28:33.175970</t>
+          <t>17 days, 22:03:04.755130</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 22:13:33.175946</t>
+          <t>17 days, 21:48:04.755092</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 22:13:33.175922</t>
+          <t>17 days, 21:48:04.755055</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3920,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 20:13:33.175898</t>
+          <t>17 days, 19:48:04.755018</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 20:13:33.175861</t>
+          <t>17 days, 19:48:04.754980</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 20:13:33.175831</t>
+          <t>17 days, 19:48:04.754939</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 20:13:33.175803</t>
+          <t>17 days, 19:48:04.754899</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18 days, 19:43:33.175779</t>
+          <t>17 days, 19:18:04.754862</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4205,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 19:43:33.175757</t>
+          <t>17 days, 19:18:04.754828</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18 days, 19:43:33.175736</t>
+          <t>17 days, 19:18:04.754795</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18 days, 19:43:33.175714</t>
+          <t>17 days, 19:18:04.754761</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4531,12 +4531,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>17 days, 14:28:33.175564</t>
+          <t>16 days, 14:03:04.754506</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>16 days, 22:28:33.175498</t>
+          <t>15 days, 22:03:04.754402</t>
         </is>
       </c>
     </row>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>16 days, 19:58:33.175467</t>
+          <t>15 days, 19:33:04.754357</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>16 days, 19:58:33.175439</t>
+          <t>15 days, 19:33:04.754315</t>
         </is>
       </c>
     </row>
@@ -4978,12 +4978,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>16 days, 19:58:33.175411</t>
+          <t>15 days, 19:33:04.754274</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>16 days, 19:58:33.175381</t>
+          <t>15 days, 19:33:04.754231</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5137,12 +5137,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5190,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5455,12 +5455,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5561,12 +5561,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5614,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5667,12 +5667,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5773,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5932,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6038,12 +6038,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6091,12 +6091,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6144,12 +6144,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6197,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6250,12 +6250,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6356,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6462,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6515,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6727,12 +6727,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6780,12 +6780,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6940,12 +6940,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6993,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7046,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7099,12 +7099,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7205,12 +7205,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7258,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7417,12 +7417,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7470,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7523,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7576,12 +7576,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7629,12 +7629,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7735,12 +7735,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7841,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -7957,12 +7957,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8073,12 +8073,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8131,12 +8131,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8305,12 +8305,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8421,12 +8421,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8479,12 +8479,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8595,12 +8595,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8653,12 +8653,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8711,12 +8711,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8769,12 +8769,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8827,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8885,12 +8885,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -8943,12 +8943,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9001,12 +9001,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9233,12 +9233,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9291,12 +9291,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9465,12 +9465,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9697,12 +9697,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9813,12 +9813,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9871,12 +9871,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -9987,12 +9987,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10045,12 +10045,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10103,12 +10103,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10161,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10219,12 +10219,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10277,12 +10277,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10451,12 +10451,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10509,12 +10509,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10567,12 +10567,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10625,12 +10625,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10683,12 +10683,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10799,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10915,12 +10915,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -10973,12 +10973,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11031,12 +11031,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11089,12 +11089,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11147,12 +11147,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11205,12 +11205,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11321,12 +11321,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11379,12 +11379,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11432,12 +11432,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11485,12 +11485,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11538,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11591,12 +11591,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11702,12 +11702,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11760,12 +11760,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11818,12 +11818,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>12 days, 19:13:33.173069</t>
+          <t>11 days, 18:48:04.750514</t>
         </is>
       </c>
     </row>
@@ -11996,12 +11996,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12054,12 +12054,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12170,12 +12170,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12228,12 +12228,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12286,12 +12286,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12344,12 +12344,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12402,12 +12402,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12460,12 +12460,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12518,12 +12518,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12576,12 +12576,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12634,12 +12634,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12692,12 +12692,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12750,12 +12750,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12866,12 +12866,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>12 days, 17:43:33.172679</t>
+          <t>11 days, 17:18:04.749890</t>
         </is>
       </c>
     </row>
@@ -12972,12 +12972,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13025,12 +13025,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13078,12 +13078,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13131,12 +13131,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13184,12 +13184,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172574</t>
+          <t>11 days, 17:03:04.749655</t>
         </is>
       </c>
     </row>
@@ -13306,12 +13306,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13369,12 +13369,12 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172534</t>
+          <t>11 days, 17:03:04.749572</t>
         </is>
       </c>
     </row>
@@ -13428,12 +13428,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -13491,12 +13491,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172497</t>
+          <t>11 days, 17:03:04.749505</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172477</t>
+          <t>11 days, 17:03:04.749471</t>
         </is>
       </c>
     </row>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172459</t>
+          <t>11 days, 17:03:04.749439</t>
         </is>
       </c>
     </row>
@@ -13680,12 +13680,12 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172441</t>
+          <t>11 days, 17:03:04.749407</t>
         </is>
       </c>
     </row>
@@ -13743,12 +13743,12 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172422</t>
+          <t>11 days, 17:03:04.749373</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172403</t>
+          <t>11 days, 17:03:04.749339</t>
         </is>
       </c>
     </row>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172383</t>
+          <t>11 days, 17:03:04.749304</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172365</t>
+          <t>11 days, 17:03:04.749272</t>
         </is>
       </c>
     </row>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172345</t>
+          <t>11 days, 17:03:04.749239</t>
         </is>
       </c>
     </row>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172328</t>
+          <t>11 days, 17:03:04.749208</t>
         </is>
       </c>
     </row>
@@ -14121,12 +14121,12 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172309</t>
+          <t>11 days, 17:03:04.749176</t>
         </is>
       </c>
     </row>
@@ -14184,12 +14184,12 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172291</t>
+          <t>11 days, 17:03:04.749145</t>
         </is>
       </c>
     </row>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172273</t>
+          <t>11 days, 17:03:04.749115</t>
         </is>
       </c>
     </row>
@@ -14310,12 +14310,12 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172255</t>
+          <t>11 days, 17:03:04.749084</t>
         </is>
       </c>
     </row>
@@ -14373,12 +14373,12 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172236</t>
+          <t>11 days, 17:03:04.749051</t>
         </is>
       </c>
     </row>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172216</t>
+          <t>11 days, 17:03:04.749017</t>
         </is>
       </c>
     </row>
@@ -14499,12 +14499,12 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172197</t>
+          <t>11 days, 17:03:04.748986</t>
         </is>
       </c>
     </row>
@@ -14562,12 +14562,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172179</t>
+          <t>11 days, 17:03:04.748955</t>
         </is>
       </c>
     </row>
@@ -14625,12 +14625,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172162</t>
+          <t>11 days, 17:03:04.748925</t>
         </is>
       </c>
     </row>
@@ -14688,12 +14688,12 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172142</t>
+          <t>11 days, 17:03:04.748894</t>
         </is>
       </c>
     </row>
@@ -14747,12 +14747,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -14810,12 +14810,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172104</t>
+          <t>11 days, 17:03:04.748827</t>
         </is>
       </c>
     </row>
@@ -14873,12 +14873,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172085</t>
+          <t>11 days, 17:03:04.748795</t>
         </is>
       </c>
     </row>
@@ -14936,12 +14936,12 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172066</t>
+          <t>11 days, 17:03:04.748763</t>
         </is>
       </c>
     </row>
@@ -14998,12 +14998,12 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172047</t>
+          <t>11 days, 17:03:04.748730</t>
         </is>
       </c>
     </row>
@@ -15057,12 +15057,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.172011</t>
+          <t>11 days, 17:03:04.748630</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171993</t>
+          <t>11 days, 17:03:04.748595</t>
         </is>
       </c>
     </row>
@@ -15241,12 +15241,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15303,12 +15303,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171944</t>
+          <t>11 days, 17:03:04.748528</t>
         </is>
       </c>
     </row>
@@ -15365,12 +15365,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171925</t>
+          <t>11 days, 17:03:04.748498</t>
         </is>
       </c>
     </row>
@@ -15423,12 +15423,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15481,12 +15481,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171850</t>
+          <t>11 days, 17:03:04.748395</t>
         </is>
       </c>
     </row>
@@ -15601,12 +15601,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15659,12 +15659,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15717,12 +15717,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15779,12 +15779,12 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171765</t>
+          <t>11 days, 17:03:04.748257</t>
         </is>
       </c>
     </row>
@@ -15841,12 +15841,12 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171739</t>
+          <t>11 days, 17:03:04.748214</t>
         </is>
       </c>
     </row>
@@ -15899,12 +15899,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -15961,12 +15961,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171698</t>
+          <t>11 days, 17:03:04.748143</t>
         </is>
       </c>
     </row>
@@ -16023,12 +16023,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171681</t>
+          <t>11 days, 17:03:04.748112</t>
         </is>
       </c>
     </row>
@@ -16085,12 +16085,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171663</t>
+          <t>11 days, 17:03:04.748082</t>
         </is>
       </c>
     </row>
@@ -16147,12 +16147,12 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171642</t>
+          <t>11 days, 17:03:04.748048</t>
         </is>
       </c>
     </row>
@@ -16209,12 +16209,12 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171621</t>
+          <t>11 days, 17:03:04.748014</t>
         </is>
       </c>
     </row>
@@ -16271,12 +16271,12 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171602</t>
+          <t>11 days, 17:03:04.747982</t>
         </is>
       </c>
     </row>
@@ -16329,12 +16329,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16387,12 +16387,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16445,12 +16445,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16503,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171496</t>
+          <t>11 days, 17:03:04.747813</t>
         </is>
       </c>
     </row>
@@ -16627,12 +16627,12 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171476</t>
+          <t>11 days, 17:03:04.747780</t>
         </is>
       </c>
     </row>
@@ -16685,12 +16685,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16743,12 +16743,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16805,12 +16805,12 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171415</t>
+          <t>11 days, 17:03:04.747653</t>
         </is>
       </c>
     </row>
@@ -16863,12 +16863,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -16925,12 +16925,12 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171373</t>
+          <t>11 days, 17:03:04.747575</t>
         </is>
       </c>
     </row>
@@ -16987,12 +16987,12 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171354</t>
+          <t>11 days, 17:03:04.747542</t>
         </is>
       </c>
     </row>
@@ -17049,12 +17049,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171337</t>
+          <t>11 days, 17:03:04.747510</t>
         </is>
       </c>
     </row>
@@ -17111,12 +17111,12 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>12 days, 17:28:33.171318</t>
+          <t>11 days, 17:03:04.747477</t>
         </is>
       </c>
     </row>
@@ -17169,12 +17169,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17227,12 +17227,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17285,12 +17285,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17343,12 +17343,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17454,12 +17454,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17507,12 +17507,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17560,12 +17560,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17613,12 +17613,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17666,12 +17666,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17719,12 +17719,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17772,12 +17772,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17825,12 +17825,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17878,12 +17878,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17931,12 +17931,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -17984,12 +17984,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18037,12 +18037,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18090,12 +18090,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18143,12 +18143,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18196,12 +18196,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18249,12 +18249,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18302,12 +18302,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18408,12 +18408,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18461,12 +18461,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18514,12 +18514,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18567,12 +18567,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18620,12 +18620,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18673,12 +18673,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18731,12 +18731,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18784,12 +18784,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18842,12 +18842,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18900,12 +18900,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -18958,12 +18958,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19016,12 +19016,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19074,12 +19074,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19132,12 +19132,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19248,12 +19248,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19306,12 +19306,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19364,12 +19364,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19422,12 +19422,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19480,12 +19480,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19538,12 +19538,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19596,12 +19596,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19654,12 +19654,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19712,12 +19712,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19765,12 +19765,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19818,12 +19818,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19871,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19924,12 +19924,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -19977,12 +19977,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20030,12 +20030,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20083,12 +20083,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20136,12 +20136,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20189,12 +20189,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20242,12 +20242,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20295,12 +20295,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20348,12 +20348,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20401,12 +20401,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20454,12 +20454,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20507,12 +20507,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20560,12 +20560,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20613,12 +20613,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20666,12 +20666,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20719,12 +20719,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20772,12 +20772,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20825,12 +20825,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20878,12 +20878,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20931,12 +20931,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -20984,12 +20984,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21037,12 +21037,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21090,12 +21090,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21143,12 +21143,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21196,12 +21196,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21249,12 +21249,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21302,12 +21302,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21355,12 +21355,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21408,12 +21408,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21514,12 +21514,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21567,12 +21567,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21620,12 +21620,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21673,12 +21673,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21726,12 +21726,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21779,12 +21779,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21832,12 +21832,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21885,12 +21885,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21938,12 +21938,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -21991,12 +21991,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22044,12 +22044,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22097,12 +22097,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22150,12 +22150,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22203,12 +22203,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22256,12 +22256,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22309,12 +22309,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22362,12 +22362,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22415,12 +22415,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22468,12 +22468,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22521,12 +22521,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22574,12 +22574,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22627,12 +22627,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22680,12 +22680,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22733,12 +22733,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22786,12 +22786,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22839,12 +22839,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22892,12 +22892,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22945,12 +22945,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -22998,12 +22998,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23104,12 +23104,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23157,12 +23157,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23210,12 +23210,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23263,12 +23263,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23316,12 +23316,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23373,12 +23373,12 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>8 days, 17:58:33.169386</t>
+          <t>7 days, 17:33:04.744138</t>
         </is>
       </c>
     </row>
@@ -23426,12 +23426,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23479,12 +23479,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23532,12 +23532,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23585,12 +23585,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23638,12 +23638,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23691,12 +23691,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23744,12 +23744,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23797,12 +23797,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23850,12 +23850,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23903,12 +23903,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -23956,12 +23956,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24009,12 +24009,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24062,12 +24062,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24115,12 +24115,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24168,12 +24168,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24274,12 +24274,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24327,12 +24327,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24433,12 +24433,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24486,12 +24486,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24539,12 +24539,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24592,12 +24592,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24645,12 +24645,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24698,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24751,12 +24751,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24804,12 +24804,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24857,12 +24857,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24910,12 +24910,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -24963,12 +24963,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25016,12 +25016,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25069,12 +25069,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25122,12 +25122,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25175,12 +25175,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25228,12 +25228,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25281,12 +25281,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25334,12 +25334,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25387,12 +25387,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25440,12 +25440,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25493,12 +25493,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25546,12 +25546,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25599,12 +25599,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25652,12 +25652,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25705,12 +25705,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25758,12 +25758,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25811,12 +25811,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25864,12 +25864,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25917,12 +25917,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -25970,12 +25970,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26023,12 +26023,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26076,12 +26076,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26129,12 +26129,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26182,12 +26182,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26235,12 +26235,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26288,12 +26288,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26341,12 +26341,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26394,12 +26394,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26447,12 +26447,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26500,12 +26500,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26553,12 +26553,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26606,12 +26606,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26659,12 +26659,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26712,12 +26712,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26765,12 +26765,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26818,12 +26818,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26871,12 +26871,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26924,12 +26924,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -26977,12 +26977,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27030,12 +27030,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27083,12 +27083,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27136,12 +27136,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27189,12 +27189,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27242,12 +27242,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27295,12 +27295,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27348,12 +27348,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27401,12 +27401,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27454,12 +27454,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27507,12 +27507,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27560,12 +27560,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27613,12 +27613,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27666,12 +27666,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27719,12 +27719,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27772,12 +27772,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27825,12 +27825,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27878,12 +27878,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27931,12 +27931,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -27984,12 +27984,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28037,12 +28037,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28090,12 +28090,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28143,12 +28143,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28196,12 +28196,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28249,12 +28249,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28302,12 +28302,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28355,12 +28355,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28408,12 +28408,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28514,12 +28514,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28567,12 +28567,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28620,12 +28620,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28673,12 +28673,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28726,12 +28726,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28779,12 +28779,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28832,12 +28832,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28885,12 +28885,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28938,12 +28938,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -28991,12 +28991,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29044,12 +29044,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29097,12 +29097,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29150,12 +29150,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29203,12 +29203,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29256,12 +29256,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29309,12 +29309,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29362,12 +29362,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29415,12 +29415,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29468,12 +29468,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29521,12 +29521,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29574,12 +29574,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29627,12 +29627,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29680,12 +29680,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29733,12 +29733,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29786,12 +29786,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29839,12 +29839,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29892,12 +29892,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29945,12 +29945,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -29998,12 +29998,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -30051,12 +30051,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
@@ -30104,12 +30104,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>10/09/26 04:46 PM</t>
+          <t>10/10/26 05:11 PM</t>
         </is>
       </c>
     </row>
